--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\売上\bigboss-special-page-claude-multi-store-sales-dashboard-4kty7j\bigboss-special-page-claude-multi-store-sales-dashboard-4kty7j\dashboard\data\incoming\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F282145-DEB9-445B-AC0D-2CE029EEC034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7189D44-C4A9-4E46-BEA9-49EC386E944C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="46">
   <si>
     <t>日付</t>
   </si>
@@ -289,10 +289,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -309,33 +312,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="桁区切り 2" xfId="1" xr:uid="{2F836AE7-868D-4DC3-9196-B836E4ADCDC8}"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -934,7 +918,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E801"/>
+  <dimension ref="A1:E907"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -967,7 +951,7 @@
       <c r="B2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2">
         <v>3671941</v>
       </c>
       <c r="D2" s="7"/>
@@ -980,7 +964,7 @@
       <c r="B3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3">
         <v>1315677</v>
       </c>
       <c r="D3" s="7"/>
@@ -993,7 +977,7 @@
       <c r="B4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4">
         <v>1512664</v>
       </c>
       <c r="D4" s="7"/>
@@ -1006,7 +990,7 @@
       <c r="B5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>4110796</v>
       </c>
       <c r="D5" s="7"/>
@@ -1019,7 +1003,7 @@
       <c r="B6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6">
         <v>23019018</v>
       </c>
       <c r="D6" s="7"/>
@@ -1032,7 +1016,7 @@
       <c r="B7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <v>3203773</v>
       </c>
       <c r="D7" s="7"/>
@@ -1045,7 +1029,7 @@
       <c r="B8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8">
         <v>3009940</v>
       </c>
       <c r="D8" s="7"/>
@@ -1058,7 +1042,7 @@
       <c r="B9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9">
         <v>2554427</v>
       </c>
       <c r="D9" s="7"/>
@@ -1071,7 +1055,7 @@
       <c r="B10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10">
         <v>2395862</v>
       </c>
       <c r="D10" s="7"/>
@@ -1084,7 +1068,7 @@
       <c r="B11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11">
         <v>18087794</v>
       </c>
       <c r="D11" s="7"/>
@@ -1097,7 +1081,7 @@
       <c r="B12" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12">
         <v>2083206</v>
       </c>
       <c r="D12" s="7"/>
@@ -1110,7 +1094,7 @@
       <c r="B13" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13">
         <v>1394813</v>
       </c>
       <c r="D13" s="7"/>
@@ -1123,1277 +1107,1855 @@
       <c r="B14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14">
         <v>1372659</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15" s="6"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="7"/>
+      <c r="A15" s="6">
+        <v>46279</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15">
+        <v>1474765</v>
+      </c>
       <c r="D15" s="7"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="6"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="6"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="6"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="6"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="6"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="5"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="6"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="6"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="6"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="6"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="5"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="6"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="6"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="5"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="6"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="5"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="6"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="6"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="6"/>
       <c r="B30" s="5"/>
-      <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="5"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="6"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="5"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="6"/>
       <c r="B32" s="5"/>
-      <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A33" s="6"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="7"/>
+      <c r="A33" s="6">
+        <v>45901</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33">
+        <v>5926563</v>
+      </c>
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="6">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="7">
-        <v>5926563</v>
+      <c r="C34">
+        <v>1999167</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="6">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="7">
-        <v>1999167</v>
+      <c r="C35">
+        <v>2262783</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="6">
-        <v>45903</v>
+        <v>45904</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="7">
-        <v>2262783</v>
+      <c r="C36">
+        <v>5638677</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="6">
-        <v>45904</v>
+        <v>45905</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C37" s="7">
-        <v>5638677</v>
+      <c r="C37">
+        <v>20611507</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="6">
-        <v>45905</v>
+        <v>45906</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="7">
-        <v>20611507</v>
+      <c r="C38">
+        <v>4464026</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="6">
-        <v>45906</v>
+        <v>45907</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="7">
-        <v>4464026</v>
+      <c r="C39">
+        <v>4387098</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="6">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="7">
-        <v>4387098</v>
+      <c r="C40">
+        <v>5231597</v>
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="6">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C41" s="7">
-        <v>5231597</v>
+      <c r="C41">
+        <v>2547384</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="6">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C42" s="7">
-        <v>2547384</v>
+      <c r="C42">
+        <v>13691536</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="6">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="7">
-        <v>13691536</v>
+      <c r="C43">
+        <v>2006513</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="6">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="7">
-        <v>2006513</v>
+      <c r="C44">
+        <v>1344978</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="6">
-        <v>45912</v>
+        <v>45913</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C45" s="7">
-        <v>1344978</v>
+      <c r="C45">
+        <v>1600435</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="6">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="7">
-        <v>1600435</v>
+      <c r="C46">
+        <v>1058783</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="6"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="7"/>
+      <c r="A47" s="6">
+        <v>45915</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47">
+        <v>2905889</v>
+      </c>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="6"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="7"/>
+      <c r="A48" s="6">
+        <v>45916</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48">
+        <v>1618459</v>
+      </c>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="6"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="7"/>
+      <c r="A49" s="6">
+        <v>45917</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49">
+        <v>1273134</v>
+      </c>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="6"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="7"/>
+      <c r="A50" s="6">
+        <v>45918</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50">
+        <v>3693978</v>
+      </c>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="6"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="7"/>
+      <c r="A51" s="6">
+        <v>45919</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51">
+        <v>2038827</v>
+      </c>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="6"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="7"/>
+      <c r="A52" s="6">
+        <v>45920</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52">
+        <v>8723486</v>
+      </c>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="6"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="7"/>
+      <c r="A53" s="6">
+        <v>45921</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53">
+        <v>2981859</v>
+      </c>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A54" s="6"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="7"/>
+      <c r="A54" s="6">
+        <v>45922</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54">
+        <v>1943219</v>
+      </c>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A55" s="6"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="7"/>
+      <c r="A55" s="6">
+        <v>45923</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55">
+        <v>2673243</v>
+      </c>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A56" s="6"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="7"/>
+      <c r="A56" s="6">
+        <v>45924</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56">
+        <v>1729033</v>
+      </c>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A57" s="6"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="7"/>
+      <c r="A57" s="6">
+        <v>45925</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C57">
+        <v>2167431</v>
+      </c>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A58" s="6"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="7"/>
+      <c r="A58" s="6">
+        <v>45926</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58">
+        <v>1100135</v>
+      </c>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A59" s="6"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="7"/>
+      <c r="A59" s="6">
+        <v>45927</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59">
+        <v>1097232</v>
+      </c>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A60" s="6"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="7"/>
+      <c r="A60" s="6">
+        <v>45928</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60">
+        <v>1189159</v>
+      </c>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="6"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="7"/>
+      <c r="A61" s="6">
+        <v>45929</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61">
+        <v>941690</v>
+      </c>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A62" s="6"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="7"/>
+      <c r="A62" s="6">
+        <v>45930</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C62">
+        <v>2918601</v>
+      </c>
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A63" s="6"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="7"/>
+      <c r="A63" s="8"/>
+      <c r="B63" s="9"/>
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A64" s="6"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="7"/>
+      <c r="A64" s="6">
+        <v>45536</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64">
+        <v>6343719</v>
+      </c>
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A65" s="6"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="7"/>
+      <c r="A65" s="6">
+        <v>45537</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C65">
+        <v>1584004</v>
+      </c>
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A66" s="6"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="7"/>
+      <c r="A66" s="6">
+        <v>45538</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66">
+        <v>1409487</v>
+      </c>
       <c r="D66" s="7"/>
       <c r="E66" s="5"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A67" s="6"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="7"/>
+      <c r="A67" s="6">
+        <v>45539</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C67">
+        <v>5780482</v>
+      </c>
       <c r="D67" s="7"/>
       <c r="E67" s="5"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A68" s="6"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="7"/>
+      <c r="A68" s="6">
+        <v>45540</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68">
+        <v>25583903</v>
+      </c>
       <c r="D68" s="7"/>
       <c r="E68" s="5"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A69" s="6"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="7"/>
+      <c r="A69" s="6">
+        <v>45541</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69">
+        <v>2688034</v>
+      </c>
       <c r="D69" s="7"/>
       <c r="E69" s="5"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A70" s="6"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="7"/>
+      <c r="A70" s="6">
+        <v>45542</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70">
+        <v>3509667</v>
+      </c>
       <c r="D70" s="7"/>
       <c r="E70" s="5"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A71" s="6"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="7"/>
+      <c r="A71" s="6">
+        <v>45543</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71">
+        <v>3679634</v>
+      </c>
       <c r="D71" s="7"/>
       <c r="E71" s="5"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A72" s="6"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="7"/>
+      <c r="A72" s="6">
+        <v>45544</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72">
+        <v>2382724</v>
+      </c>
       <c r="D72" s="7"/>
       <c r="E72" s="5"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A73" s="6"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="7"/>
+      <c r="A73" s="6">
+        <v>45545</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73">
+        <v>14145904</v>
+      </c>
       <c r="D73" s="7"/>
       <c r="E73" s="5"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A74" s="6"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="7"/>
+      <c r="A74" s="6">
+        <v>45546</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C74">
+        <v>1930658</v>
+      </c>
       <c r="D74" s="7"/>
       <c r="E74" s="5"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A75" s="6"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="7"/>
+      <c r="A75" s="6">
+        <v>45547</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75">
+        <v>1478134</v>
+      </c>
       <c r="D75" s="7"/>
       <c r="E75" s="5"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A76" s="6"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="7"/>
+      <c r="A76" s="6">
+        <v>45548</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C76">
+        <v>1095766</v>
+      </c>
       <c r="D76" s="7"/>
       <c r="E76" s="5"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A77" s="6"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="7"/>
+      <c r="A77" s="6">
+        <v>45549</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77">
+        <v>1159627</v>
+      </c>
       <c r="D77" s="7"/>
       <c r="E77" s="5"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A78" s="6"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="7"/>
+      <c r="A78" s="6">
+        <v>45550</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C78">
+        <v>3353887</v>
+      </c>
       <c r="D78" s="7"/>
       <c r="E78" s="5"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A79" s="6"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="7"/>
+      <c r="A79" s="6">
+        <v>45551</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79">
+        <v>1435217</v>
+      </c>
       <c r="D79" s="7"/>
       <c r="E79" s="5"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A80" s="6"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="7"/>
+      <c r="A80" s="6">
+        <v>45552</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C80">
+        <v>1948031</v>
+      </c>
       <c r="D80" s="7"/>
       <c r="E80" s="5"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A81" s="6"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="7"/>
+      <c r="A81" s="6">
+        <v>45553</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C81">
+        <v>3202230</v>
+      </c>
       <c r="D81" s="7"/>
       <c r="E81" s="5"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A82" s="6"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="7"/>
+      <c r="A82" s="6">
+        <v>45554</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C82">
+        <v>2423331</v>
+      </c>
       <c r="D82" s="7"/>
       <c r="E82" s="5"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A83" s="6"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="7"/>
+      <c r="A83" s="6">
+        <v>45555</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C83">
+        <v>6928045</v>
+      </c>
       <c r="D83" s="7"/>
       <c r="E83" s="5"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A84" s="6"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="7"/>
+      <c r="A84" s="6">
+        <v>45556</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C84">
+        <v>2102205</v>
+      </c>
       <c r="D84" s="7"/>
       <c r="E84" s="5"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A85" s="6"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="7"/>
+      <c r="A85" s="6">
+        <v>45557</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C85">
+        <v>1841570</v>
+      </c>
       <c r="D85" s="7"/>
       <c r="E85" s="5"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A86" s="6"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="7"/>
+      <c r="A86" s="6">
+        <v>45558</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C86">
+        <v>3555918</v>
+      </c>
       <c r="D86" s="7"/>
       <c r="E86" s="5"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A87" s="6"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="7"/>
+      <c r="A87" s="6">
+        <v>45559</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C87">
+        <v>1263132</v>
+      </c>
       <c r="D87" s="7"/>
       <c r="E87" s="5"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A88" s="6"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="7"/>
+      <c r="A88" s="6">
+        <v>45560</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C88">
+        <v>2213905</v>
+      </c>
       <c r="D88" s="7"/>
       <c r="E88" s="5"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A89" s="6"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="7"/>
+      <c r="A89" s="6">
+        <v>45561</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C89">
+        <v>1733236</v>
+      </c>
       <c r="D89" s="7"/>
       <c r="E89" s="5"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A90" s="6"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="7"/>
+      <c r="A90" s="6">
+        <v>45562</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C90">
+        <v>1299072</v>
+      </c>
       <c r="D90" s="7"/>
       <c r="E90" s="5"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A91" s="6"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="7"/>
+      <c r="A91" s="6">
+        <v>45563</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C91">
+        <v>1051107</v>
+      </c>
       <c r="D91" s="7"/>
       <c r="E91" s="5"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A92" s="6"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="7"/>
+      <c r="A92" s="6">
+        <v>45564</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92">
+        <v>1456792</v>
+      </c>
       <c r="D92" s="7"/>
       <c r="E92" s="5"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A93" s="6"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="7"/>
+      <c r="A93" s="6">
+        <v>45565</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C93">
+        <v>2580396</v>
+      </c>
       <c r="D93" s="7"/>
       <c r="E93" s="5"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A94" s="6"/>
-      <c r="B94" s="5"/>
-      <c r="C94" s="7"/>
+      <c r="A94" s="8"/>
+      <c r="B94" s="9"/>
       <c r="D94" s="7"/>
       <c r="E94" s="5"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A95" s="6"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="7"/>
+      <c r="A95" s="6">
+        <v>45170</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C95">
+        <v>5252965</v>
+      </c>
       <c r="D95" s="7"/>
       <c r="E95" s="5"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A96" s="6"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="7"/>
+      <c r="A96" s="6">
+        <v>45171</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C96">
+        <v>1260652</v>
+      </c>
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A97" s="6"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="7"/>
+      <c r="A97" s="6">
+        <v>45172</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C97">
+        <v>897521</v>
+      </c>
       <c r="D97" s="7"/>
       <c r="E97" s="5"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A98" s="6"/>
-      <c r="B98" s="5"/>
-      <c r="C98" s="7"/>
+      <c r="A98" s="6">
+        <v>45173</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C98">
+        <v>3990733</v>
+      </c>
       <c r="D98" s="7"/>
       <c r="E98" s="5"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A99" s="6"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="7"/>
+      <c r="A99" s="6">
+        <v>45174</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C99">
+        <v>19951151</v>
+      </c>
       <c r="D99" s="7"/>
       <c r="E99" s="5"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A100" s="6"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="7"/>
+      <c r="A100" s="6">
+        <v>45175</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C100">
+        <v>1490798</v>
+      </c>
       <c r="D100" s="7"/>
       <c r="E100" s="5"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A101" s="6"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="7"/>
+      <c r="A101" s="6">
+        <v>45176</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C101">
+        <v>1029945</v>
+      </c>
       <c r="D101" s="7"/>
       <c r="E101" s="5"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A102" s="6"/>
-      <c r="B102" s="5"/>
-      <c r="C102" s="7"/>
+      <c r="A102" s="6">
+        <v>45177</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C102">
+        <v>789607</v>
+      </c>
       <c r="D102" s="7"/>
       <c r="E102" s="5"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A103" s="6"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="7"/>
+      <c r="A103" s="6">
+        <v>45178</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C103">
+        <v>1557750</v>
+      </c>
       <c r="D103" s="7"/>
       <c r="E103" s="5"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A104" s="6"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="7"/>
+      <c r="A104" s="6">
+        <v>45179</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C104">
+        <v>14510958</v>
+      </c>
       <c r="D104" s="7"/>
       <c r="E104" s="5"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A105" s="6"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="7"/>
+      <c r="A105" s="6">
+        <v>45180</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C105">
+        <v>1388565</v>
+      </c>
       <c r="D105" s="7"/>
       <c r="E105" s="5"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A106" s="6"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="7"/>
+      <c r="A106" s="6">
+        <v>45181</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C106">
+        <v>1073210</v>
+      </c>
       <c r="D106" s="7"/>
       <c r="E106" s="5"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A107" s="6"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="7"/>
+      <c r="A107" s="6">
+        <v>45182</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C107">
+        <v>1051743</v>
+      </c>
       <c r="D107" s="7"/>
       <c r="E107" s="5"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A108" s="6"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="7"/>
+      <c r="A108" s="6">
+        <v>45183</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C108">
+        <v>823874</v>
+      </c>
       <c r="D108" s="7"/>
       <c r="E108" s="5"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A109" s="6"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="7"/>
+      <c r="A109" s="6">
+        <v>45184</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C109">
+        <v>2486983</v>
+      </c>
       <c r="D109" s="7"/>
       <c r="E109" s="5"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A110" s="6"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="7"/>
+      <c r="A110" s="6">
+        <v>45185</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C110">
+        <v>1031798</v>
+      </c>
       <c r="D110" s="7"/>
       <c r="E110" s="5"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A111" s="6"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="7"/>
+      <c r="A111" s="6">
+        <v>45186</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C111">
+        <v>1177948</v>
+      </c>
       <c r="D111" s="7"/>
       <c r="E111" s="5"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A112" s="6"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="7"/>
+      <c r="A112" s="6">
+        <v>45187</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C112">
+        <v>1410129</v>
+      </c>
       <c r="D112" s="7"/>
       <c r="E112" s="5"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A113" s="6"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="7"/>
+      <c r="A113" s="6">
+        <v>45188</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C113">
+        <v>1560839</v>
+      </c>
       <c r="D113" s="7"/>
       <c r="E113" s="5"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A114" s="6"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="7"/>
+      <c r="A114" s="6">
+        <v>45189</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C114">
+        <v>15873506</v>
+      </c>
       <c r="D114" s="7"/>
       <c r="E114" s="5"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A115" s="6"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="7"/>
+      <c r="A115" s="6">
+        <v>45190</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C115">
+        <v>1640100</v>
+      </c>
       <c r="D115" s="7"/>
       <c r="E115" s="5"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A116" s="6"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="7"/>
+      <c r="A116" s="6">
+        <v>45191</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C116">
+        <v>1098015</v>
+      </c>
       <c r="D116" s="7"/>
       <c r="E116" s="5"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A117" s="6"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="7"/>
+      <c r="A117" s="6">
+        <v>45192</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C117">
+        <v>1768601</v>
+      </c>
       <c r="D117" s="7"/>
       <c r="E117" s="5"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A118" s="6"/>
-      <c r="B118" s="5"/>
-      <c r="C118" s="7"/>
+      <c r="A118" s="6">
+        <v>45193</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C118">
+        <v>946881</v>
+      </c>
       <c r="D118" s="7"/>
       <c r="E118" s="5"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A119" s="6"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="7"/>
+      <c r="A119" s="6">
+        <v>45194</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C119">
+        <v>3187934</v>
+      </c>
       <c r="D119" s="7"/>
       <c r="E119" s="5"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A120" s="6"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="7"/>
+      <c r="A120" s="6">
+        <v>45195</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C120">
+        <v>887372</v>
+      </c>
       <c r="D120" s="7"/>
       <c r="E120" s="5"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A121" s="6"/>
-      <c r="B121" s="5"/>
-      <c r="C121" s="7"/>
+      <c r="A121" s="6">
+        <v>45196</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C121">
+        <v>1006118</v>
+      </c>
       <c r="D121" s="7"/>
       <c r="E121" s="5"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A122" s="6"/>
-      <c r="B122" s="5"/>
-      <c r="C122" s="7"/>
+      <c r="A122" s="6">
+        <v>45197</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C122">
+        <v>823154</v>
+      </c>
       <c r="D122" s="7"/>
       <c r="E122" s="5"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A123" s="6"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="7"/>
+      <c r="A123" s="6">
+        <v>45198</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C123">
+        <v>1065172</v>
+      </c>
       <c r="D123" s="7"/>
       <c r="E123" s="5"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A124" s="6"/>
-      <c r="B124" s="5"/>
-      <c r="C124" s="7"/>
+      <c r="A124" s="6">
+        <v>45199</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C124">
+        <v>2307189</v>
+      </c>
       <c r="D124" s="7"/>
       <c r="E124" s="5"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A125" s="6"/>
-      <c r="B125" s="5"/>
-      <c r="C125" s="7"/>
+      <c r="A125" s="8"/>
+      <c r="B125" s="9"/>
       <c r="D125" s="7"/>
       <c r="E125" s="5"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A126" s="6"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="7"/>
+      <c r="A126" s="8"/>
+      <c r="B126" s="9"/>
       <c r="D126" s="7"/>
       <c r="E126" s="5"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A127" s="6"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="7"/>
+      <c r="A127" s="8"/>
+      <c r="B127" s="9"/>
       <c r="D127" s="7"/>
       <c r="E127" s="5"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A128" s="6"/>
-      <c r="B128" s="5"/>
-      <c r="C128" s="7"/>
+      <c r="A128" s="8"/>
+      <c r="B128" s="9"/>
       <c r="D128" s="7"/>
       <c r="E128" s="5"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A129" s="6"/>
-      <c r="B129" s="5"/>
-      <c r="C129" s="7"/>
+      <c r="A129" s="8"/>
+      <c r="B129" s="9"/>
       <c r="D129" s="7"/>
       <c r="E129" s="5"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A130" s="6"/>
-      <c r="B130" s="5"/>
-      <c r="C130" s="7"/>
+      <c r="A130" s="8"/>
+      <c r="B130" s="9"/>
       <c r="D130" s="7"/>
       <c r="E130" s="5"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A131" s="6"/>
-      <c r="B131" s="5"/>
-      <c r="C131" s="7"/>
+      <c r="A131" s="8"/>
+      <c r="B131" s="9"/>
       <c r="D131" s="7"/>
       <c r="E131" s="5"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A132" s="6"/>
-      <c r="B132" s="5"/>
-      <c r="C132" s="7"/>
+      <c r="A132" s="8"/>
+      <c r="B132" s="9"/>
       <c r="D132" s="7"/>
       <c r="E132" s="5"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A133" s="6"/>
-      <c r="B133" s="5"/>
-      <c r="C133" s="7"/>
+      <c r="A133" s="8"/>
+      <c r="B133" s="9"/>
       <c r="D133" s="7"/>
       <c r="E133" s="5"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A134" s="6"/>
-      <c r="B134" s="5"/>
-      <c r="C134" s="7"/>
+      <c r="A134" s="8"/>
+      <c r="B134" s="9"/>
       <c r="D134" s="7"/>
       <c r="E134" s="5"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A135" s="6"/>
-      <c r="B135" s="5"/>
-      <c r="C135" s="7"/>
+      <c r="A135" s="8"/>
+      <c r="B135" s="9"/>
       <c r="D135" s="7"/>
       <c r="E135" s="5"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A136" s="6"/>
-      <c r="B136" s="5"/>
-      <c r="C136" s="7"/>
+      <c r="A136" s="8"/>
+      <c r="B136" s="9"/>
       <c r="D136" s="7"/>
       <c r="E136" s="5"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A137" s="6"/>
-      <c r="B137" s="5"/>
-      <c r="C137" s="7"/>
+      <c r="A137" s="8"/>
+      <c r="B137" s="9"/>
       <c r="D137" s="7"/>
       <c r="E137" s="5"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A138" s="6"/>
-      <c r="B138" s="5"/>
-      <c r="C138" s="7"/>
+      <c r="A138" s="8"/>
+      <c r="B138" s="9"/>
       <c r="D138" s="7"/>
       <c r="E138" s="5"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A139" s="6"/>
-      <c r="B139" s="5"/>
-      <c r="C139" s="7"/>
+      <c r="A139" s="8"/>
+      <c r="B139" s="9"/>
       <c r="D139" s="7"/>
       <c r="E139" s="5"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A140" s="6"/>
-      <c r="B140" s="5"/>
-      <c r="C140" s="7"/>
       <c r="D140" s="7"/>
       <c r="E140" s="5"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A141" s="6"/>
-      <c r="B141" s="5"/>
-      <c r="C141" s="7"/>
       <c r="D141" s="7"/>
       <c r="E141" s="5"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A142" s="6"/>
-      <c r="B142" s="5"/>
-      <c r="C142" s="7"/>
       <c r="D142" s="7"/>
       <c r="E142" s="5"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A143" s="6"/>
-      <c r="B143" s="5"/>
-      <c r="C143" s="7"/>
       <c r="D143" s="7"/>
       <c r="E143" s="5"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A144" s="6"/>
-      <c r="B144" s="5"/>
-      <c r="C144" s="7"/>
       <c r="D144" s="7"/>
       <c r="E144" s="5"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A145" s="6"/>
-      <c r="B145" s="5"/>
-      <c r="C145" s="7"/>
       <c r="D145" s="7"/>
       <c r="E145" s="5"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A146" s="6"/>
-      <c r="B146" s="5"/>
-      <c r="C146" s="7"/>
       <c r="D146" s="7"/>
       <c r="E146" s="5"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A147" s="6"/>
-      <c r="B147" s="5"/>
-      <c r="C147" s="7"/>
       <c r="D147" s="7"/>
       <c r="E147" s="5"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A148" s="6"/>
-      <c r="B148" s="5"/>
-      <c r="C148" s="7"/>
       <c r="D148" s="7"/>
       <c r="E148" s="5"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A149" s="6"/>
-      <c r="B149" s="5"/>
-      <c r="C149" s="7"/>
       <c r="D149" s="7"/>
       <c r="E149" s="5"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A150" s="6"/>
-      <c r="B150" s="5"/>
-      <c r="C150" s="7"/>
       <c r="D150" s="7"/>
       <c r="E150" s="5"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A151" s="6"/>
-      <c r="B151" s="5"/>
-      <c r="C151" s="7"/>
       <c r="D151" s="7"/>
       <c r="E151" s="5"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A152" s="6"/>
-      <c r="B152" s="5"/>
-      <c r="C152" s="7"/>
       <c r="D152" s="7"/>
       <c r="E152" s="5"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A153" s="6"/>
-      <c r="B153" s="5"/>
-      <c r="C153" s="7"/>
       <c r="D153" s="7"/>
       <c r="E153" s="5"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A154" s="6"/>
-      <c r="B154" s="5"/>
-      <c r="C154" s="7"/>
+      <c r="A154" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C154" s="7">
+        <v>5275514</v>
+      </c>
       <c r="D154" s="7"/>
       <c r="E154" s="5"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A155" s="6"/>
-      <c r="B155" s="5"/>
-      <c r="C155" s="7"/>
+      <c r="A155" s="6">
+        <v>46236</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C155" s="7">
+        <v>2707755</v>
+      </c>
       <c r="D155" s="7"/>
       <c r="E155" s="5"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A156" s="6"/>
-      <c r="B156" s="5"/>
-      <c r="C156" s="7"/>
+      <c r="A156" s="6">
+        <v>46237</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C156" s="7">
+        <v>2422922</v>
+      </c>
       <c r="D156" s="7"/>
       <c r="E156" s="5"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A157" s="6"/>
-      <c r="B157" s="5"/>
-      <c r="C157" s="7"/>
+      <c r="A157" s="6">
+        <v>46238</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C157" s="7">
+        <v>3782438</v>
+      </c>
       <c r="D157" s="7"/>
       <c r="E157" s="5"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A158" s="6"/>
-      <c r="B158" s="5"/>
-      <c r="C158" s="7"/>
+      <c r="A158" s="6">
+        <v>46239</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C158" s="7">
+        <v>16502417</v>
+      </c>
       <c r="D158" s="7"/>
       <c r="E158" s="5"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A159" s="6"/>
-      <c r="B159" s="5"/>
-      <c r="C159" s="7"/>
+      <c r="A159" s="6">
+        <v>46240</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C159" s="7">
+        <v>3153737</v>
+      </c>
       <c r="D159" s="7"/>
       <c r="E159" s="5"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A160" s="6"/>
-      <c r="B160" s="5"/>
-      <c r="C160" s="7"/>
+      <c r="A160" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C160" s="7">
+        <v>3971919</v>
+      </c>
       <c r="D160" s="7"/>
       <c r="E160" s="5"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A161" s="6"/>
-      <c r="B161" s="5"/>
-      <c r="C161" s="7"/>
+      <c r="A161" s="6">
+        <v>46242</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C161" s="7">
+        <v>3608563</v>
+      </c>
       <c r="D161" s="7"/>
       <c r="E161" s="5"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A162" s="6"/>
-      <c r="B162" s="5"/>
-      <c r="C162" s="7"/>
+      <c r="A162" s="6">
+        <v>46243</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C162" s="7">
+        <v>4841605</v>
+      </c>
       <c r="D162" s="7"/>
       <c r="E162" s="5"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A163" s="6"/>
-      <c r="B163" s="5"/>
-      <c r="C163" s="7"/>
+      <c r="A163" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C163" s="7">
+        <v>10777165</v>
+      </c>
       <c r="D163" s="7"/>
       <c r="E163" s="5"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A164" s="6"/>
-      <c r="B164" s="5"/>
-      <c r="C164" s="7"/>
+      <c r="A164" s="6">
+        <v>46245</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C164" s="7">
+        <v>2740219</v>
+      </c>
       <c r="D164" s="7"/>
       <c r="E164" s="5"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A165" s="6"/>
-      <c r="B165" s="5"/>
-      <c r="C165" s="7"/>
+      <c r="A165" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C165" s="7">
+        <v>1894525</v>
+      </c>
       <c r="D165" s="7"/>
       <c r="E165" s="5"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A166" s="6"/>
-      <c r="B166" s="5"/>
-      <c r="C166" s="7"/>
+      <c r="A166" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C166" s="7">
+        <v>2030053</v>
+      </c>
       <c r="D166" s="7"/>
       <c r="E166" s="5"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A167" s="6"/>
-      <c r="B167" s="5"/>
-      <c r="C167" s="7"/>
+      <c r="A167" s="6">
+        <v>46248</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C167" s="7">
+        <v>1406419</v>
+      </c>
       <c r="D167" s="7"/>
       <c r="E167" s="5"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A168" s="6"/>
-      <c r="B168" s="5"/>
-      <c r="C168" s="7"/>
+      <c r="A168" s="6">
+        <v>46249</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C168" s="7">
+        <v>5183664</v>
+      </c>
       <c r="D168" s="7"/>
       <c r="E168" s="5"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A169" s="6"/>
-      <c r="B169" s="5"/>
-      <c r="C169" s="7"/>
+      <c r="A169" s="6">
+        <v>46250</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C169" s="7">
+        <v>2508947</v>
+      </c>
       <c r="D169" s="7"/>
       <c r="E169" s="5"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A170" s="6"/>
-      <c r="B170" s="5"/>
-      <c r="C170" s="7"/>
+      <c r="A170" s="6">
+        <v>46251</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C170" s="7">
+        <v>2043059</v>
+      </c>
       <c r="D170" s="7"/>
       <c r="E170" s="5"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A171" s="6"/>
-      <c r="B171" s="5"/>
-      <c r="C171" s="7"/>
+      <c r="A171" s="6">
+        <v>46252</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C171" s="7">
+        <v>7509928</v>
+      </c>
       <c r="D171" s="7"/>
       <c r="E171" s="5"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A172" s="6"/>
-      <c r="B172" s="5"/>
-      <c r="C172" s="7"/>
+      <c r="A172" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C172" s="7">
+        <v>2555051</v>
+      </c>
       <c r="D172" s="7"/>
       <c r="E172" s="5"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A173" s="6"/>
-      <c r="B173" s="5"/>
-      <c r="C173" s="7"/>
+      <c r="A173" s="6">
+        <v>46254</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C173" s="7">
+        <v>5363467</v>
+      </c>
       <c r="D173" s="7"/>
       <c r="E173" s="5"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A174" s="6"/>
-      <c r="B174" s="5"/>
-      <c r="C174" s="7"/>
+      <c r="A174" s="6">
+        <v>46255</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C174" s="7">
+        <v>1361027</v>
+      </c>
       <c r="D174" s="7"/>
       <c r="E174" s="5"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A175" s="6"/>
-      <c r="B175" s="5"/>
-      <c r="C175" s="7"/>
+      <c r="A175" s="6">
+        <v>46256</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C175" s="7">
+        <v>1404553</v>
+      </c>
       <c r="D175" s="7"/>
       <c r="E175" s="5"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A176" s="6"/>
-      <c r="B176" s="5"/>
-      <c r="C176" s="7"/>
+      <c r="A176" s="6">
+        <v>46257</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C176" s="7">
+        <v>1666190</v>
+      </c>
       <c r="D176" s="7"/>
       <c r="E176" s="5"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A177" s="6"/>
-      <c r="B177" s="5"/>
-      <c r="C177" s="7"/>
+      <c r="A177" s="6">
+        <v>46258</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C177" s="7">
+        <v>2762985</v>
+      </c>
       <c r="D177" s="7"/>
       <c r="E177" s="5"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A178" s="6"/>
-      <c r="B178" s="5"/>
-      <c r="C178" s="7"/>
+      <c r="A178" s="6">
+        <v>46259</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C178" s="7">
+        <v>12274704</v>
+      </c>
       <c r="D178" s="7"/>
       <c r="E178" s="5"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A179" s="6"/>
-      <c r="B179" s="5"/>
-      <c r="C179" s="7"/>
+      <c r="A179" s="6">
+        <v>46260</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C179" s="7">
+        <v>4173383</v>
+      </c>
       <c r="D179" s="7"/>
       <c r="E179" s="5"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A180" s="6"/>
-      <c r="B180" s="5"/>
-      <c r="C180" s="7"/>
+      <c r="A180" s="6">
+        <v>46261</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C180" s="7">
+        <v>2679926</v>
+      </c>
       <c r="D180" s="7"/>
       <c r="E180" s="5"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A181" s="6"/>
-      <c r="B181" s="5"/>
-      <c r="C181" s="7"/>
+      <c r="A181" s="6">
+        <v>46262</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C181" s="7">
+        <v>1387635</v>
+      </c>
       <c r="D181" s="7"/>
       <c r="E181" s="5"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A182" s="6"/>
-      <c r="B182" s="5"/>
-      <c r="C182" s="7"/>
+      <c r="A182" s="6">
+        <v>46263</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C182" s="7">
+        <v>1878426</v>
+      </c>
       <c r="D182" s="7"/>
       <c r="E182" s="5"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A183" s="6"/>
-      <c r="B183" s="5"/>
-      <c r="C183" s="7"/>
+      <c r="A183" s="6">
+        <v>46264</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C183" s="7">
+        <v>3438459</v>
+      </c>
       <c r="D183" s="7"/>
       <c r="E183" s="5"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A184" s="6"/>
-      <c r="B184" s="5"/>
-      <c r="C184" s="7"/>
+      <c r="A184" s="6">
+        <v>46265</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C184" s="7">
+        <v>1440684</v>
+      </c>
       <c r="D184" s="7"/>
       <c r="E184" s="5"/>
     </row>
@@ -2405,219 +2967,405 @@
       <c r="E185" s="5"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A186" s="6"/>
-      <c r="B186" s="5"/>
-      <c r="C186" s="7"/>
+      <c r="A186" s="6">
+        <v>45870</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C186" s="7">
+        <v>7822510</v>
+      </c>
       <c r="D186" s="7"/>
       <c r="E186" s="5"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A187" s="6"/>
-      <c r="B187" s="5"/>
-      <c r="C187" s="7"/>
+      <c r="A187" s="6">
+        <v>45871</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C187" s="7">
+        <v>4237077</v>
+      </c>
       <c r="D187" s="7"/>
       <c r="E187" s="5"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A188" s="6"/>
-      <c r="B188" s="5"/>
-      <c r="C188" s="7"/>
+      <c r="A188" s="6">
+        <v>45872</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C188" s="7">
+        <v>3756441</v>
+      </c>
       <c r="D188" s="7"/>
       <c r="E188" s="5"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A189" s="6"/>
-      <c r="B189" s="5"/>
-      <c r="C189" s="7"/>
+      <c r="A189" s="6">
+        <v>45873</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C189" s="7">
+        <v>4227615</v>
+      </c>
       <c r="D189" s="7"/>
       <c r="E189" s="5"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A190" s="6"/>
-      <c r="B190" s="5"/>
-      <c r="C190" s="7"/>
+      <c r="A190" s="6">
+        <v>45874</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C190" s="7">
+        <v>17118945</v>
+      </c>
       <c r="D190" s="7"/>
       <c r="E190" s="5"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A191" s="6"/>
-      <c r="B191" s="5"/>
-      <c r="C191" s="7"/>
+      <c r="A191" s="6">
+        <v>45875</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C191" s="7">
+        <v>4164507</v>
+      </c>
       <c r="D191" s="7"/>
       <c r="E191" s="5"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A192" s="6"/>
-      <c r="B192" s="5"/>
-      <c r="C192" s="7"/>
+      <c r="A192" s="6">
+        <v>45876</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C192" s="7">
+        <v>3815286</v>
+      </c>
       <c r="D192" s="7"/>
       <c r="E192" s="5"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A193" s="6"/>
-      <c r="B193" s="5"/>
-      <c r="C193" s="7"/>
+      <c r="A193" s="6">
+        <v>45877</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C193" s="7">
+        <v>3184173</v>
+      </c>
       <c r="D193" s="7"/>
       <c r="E193" s="5"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A194" s="6"/>
-      <c r="B194" s="5"/>
-      <c r="C194" s="7"/>
+      <c r="A194" s="6">
+        <v>45878</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C194" s="7">
+        <v>3020932</v>
+      </c>
       <c r="D194" s="7"/>
       <c r="E194" s="5"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A195" s="6"/>
-      <c r="B195" s="5"/>
-      <c r="C195" s="7"/>
+      <c r="A195" s="6">
+        <v>45879</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C195" s="7">
+        <v>12398653</v>
+      </c>
       <c r="D195" s="7"/>
       <c r="E195" s="5"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A196" s="6"/>
-      <c r="B196" s="5"/>
-      <c r="C196" s="7"/>
+      <c r="A196" s="6">
+        <v>45880</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C196" s="7">
+        <v>2524451</v>
+      </c>
       <c r="D196" s="7"/>
       <c r="E196" s="5"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A197" s="6"/>
-      <c r="B197" s="5"/>
-      <c r="C197" s="7"/>
+      <c r="A197" s="6">
+        <v>45881</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C197" s="7">
+        <v>1646711</v>
+      </c>
       <c r="D197" s="7"/>
       <c r="E197" s="5"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A198" s="6"/>
-      <c r="B198" s="5"/>
-      <c r="C198" s="7"/>
+      <c r="A198" s="6">
+        <v>45882</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C198" s="7">
+        <v>1515931</v>
+      </c>
       <c r="D198" s="7"/>
       <c r="E198" s="5"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A199" s="6"/>
-      <c r="B199" s="5"/>
-      <c r="C199" s="7"/>
+      <c r="A199" s="6">
+        <v>45883</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C199" s="7">
+        <v>1312815</v>
+      </c>
       <c r="D199" s="7"/>
       <c r="E199" s="5"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A200" s="6"/>
-      <c r="B200" s="5"/>
-      <c r="C200" s="7"/>
+      <c r="A200" s="6">
+        <v>45884</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C200" s="7">
+        <v>4025688</v>
+      </c>
       <c r="D200" s="7"/>
       <c r="E200" s="5"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A201" s="6"/>
-      <c r="B201" s="5"/>
-      <c r="C201" s="7"/>
+      <c r="A201" s="6">
+        <v>45885</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C201" s="7">
+        <v>2123507</v>
+      </c>
       <c r="D201" s="7"/>
       <c r="E201" s="5"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A202" s="6"/>
-      <c r="B202" s="5"/>
-      <c r="C202" s="7"/>
+      <c r="A202" s="6">
+        <v>45886</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C202" s="7">
+        <v>2208651</v>
+      </c>
       <c r="D202" s="7"/>
       <c r="E202" s="5"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A203" s="6"/>
-      <c r="B203" s="5"/>
-      <c r="C203" s="7"/>
+      <c r="A203" s="6">
+        <v>45887</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C203" s="7">
+        <v>6098837</v>
+      </c>
       <c r="D203" s="7"/>
       <c r="E203" s="5"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A204" s="6"/>
-      <c r="B204" s="5"/>
-      <c r="C204" s="7"/>
+      <c r="A204" s="6">
+        <v>45888</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C204" s="7">
+        <v>2888045</v>
+      </c>
       <c r="D204" s="7"/>
       <c r="E204" s="5"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A205" s="6"/>
-      <c r="B205" s="5"/>
-      <c r="C205" s="7"/>
+      <c r="A205" s="6">
+        <v>45889</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C205" s="7">
+        <v>6196851</v>
+      </c>
       <c r="D205" s="7"/>
       <c r="E205" s="5"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A206" s="6"/>
-      <c r="B206" s="5"/>
-      <c r="C206" s="7"/>
+      <c r="A206" s="6">
+        <v>45890</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C206" s="7">
+        <v>2287707</v>
+      </c>
       <c r="D206" s="7"/>
       <c r="E206" s="5"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A207" s="6"/>
-      <c r="B207" s="5"/>
-      <c r="C207" s="7"/>
+      <c r="A207" s="6">
+        <v>45891</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C207" s="7">
+        <v>1776662</v>
+      </c>
       <c r="D207" s="7"/>
       <c r="E207" s="5"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A208" s="6"/>
-      <c r="B208" s="5"/>
-      <c r="C208" s="7"/>
+      <c r="A208" s="6">
+        <v>45892</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C208" s="7">
+        <v>1539594</v>
+      </c>
       <c r="D208" s="7"/>
       <c r="E208" s="5"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A209" s="6"/>
-      <c r="B209" s="5"/>
-      <c r="C209" s="7"/>
+      <c r="A209" s="6">
+        <v>45893</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C209" s="7">
+        <v>2767829</v>
+      </c>
       <c r="D209" s="7"/>
       <c r="E209" s="5"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A210" s="6"/>
-      <c r="B210" s="5"/>
-      <c r="C210" s="7"/>
+      <c r="A210" s="6">
+        <v>45894</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C210" s="7">
+        <v>9867487</v>
+      </c>
       <c r="D210" s="7"/>
       <c r="E210" s="5"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A211" s="6"/>
-      <c r="B211" s="5"/>
-      <c r="C211" s="7"/>
+      <c r="A211" s="6">
+        <v>45895</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C211" s="7">
+        <v>3213393</v>
+      </c>
       <c r="D211" s="7"/>
       <c r="E211" s="5"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A212" s="6"/>
-      <c r="B212" s="5"/>
-      <c r="C212" s="7"/>
+      <c r="A212" s="6">
+        <v>45896</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C212" s="7">
+        <v>2556628</v>
+      </c>
       <c r="D212" s="7"/>
       <c r="E212" s="5"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A213" s="6"/>
-      <c r="B213" s="5"/>
-      <c r="C213" s="7"/>
+      <c r="A213" s="6">
+        <v>45897</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C213" s="7">
+        <v>1329557</v>
+      </c>
       <c r="D213" s="7"/>
       <c r="E213" s="5"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A214" s="6"/>
-      <c r="B214" s="5"/>
-      <c r="C214" s="7"/>
+      <c r="A214" s="6">
+        <v>45898</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C214" s="7">
+        <v>1083765</v>
+      </c>
       <c r="D214" s="7"/>
       <c r="E214" s="5"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A215" s="6"/>
-      <c r="B215" s="5"/>
-      <c r="C215" s="7"/>
+      <c r="A215" s="6">
+        <v>45899</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C215" s="7">
+        <v>2282133</v>
+      </c>
       <c r="D215" s="7"/>
       <c r="E215" s="5"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A216" s="6"/>
-      <c r="B216" s="5"/>
-      <c r="C216" s="7"/>
+      <c r="A216" s="6">
+        <v>45900</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C216" s="7">
+        <v>1691484</v>
+      </c>
       <c r="D216" s="7"/>
       <c r="E216" s="5"/>
     </row>
@@ -2629,219 +3377,405 @@
       <c r="E217" s="5"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A218" s="6"/>
-      <c r="B218" s="5"/>
-      <c r="C218" s="7"/>
+      <c r="A218" s="6">
+        <v>45505</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C218" s="7">
+        <v>9802635</v>
+      </c>
       <c r="D218" s="7"/>
       <c r="E218" s="5"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A219" s="6"/>
-      <c r="B219" s="5"/>
-      <c r="C219" s="7"/>
+      <c r="A219" s="6">
+        <v>45506</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C219" s="7">
+        <v>2389182</v>
+      </c>
       <c r="D219" s="7"/>
       <c r="E219" s="5"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A220" s="6"/>
-      <c r="B220" s="5"/>
-      <c r="C220" s="7"/>
+      <c r="A220" s="6">
+        <v>45507</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C220" s="7">
+        <v>2025192</v>
+      </c>
       <c r="D220" s="7"/>
       <c r="E220" s="5"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A221" s="6"/>
-      <c r="B221" s="5"/>
-      <c r="C221" s="7"/>
+      <c r="A221" s="6">
+        <v>45508</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C221" s="7">
+        <v>4282469</v>
+      </c>
       <c r="D221" s="7"/>
       <c r="E221" s="5"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A222" s="6"/>
-      <c r="B222" s="5"/>
-      <c r="C222" s="7"/>
+      <c r="A222" s="6">
+        <v>45509</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C222" s="7">
+        <v>22330772</v>
+      </c>
       <c r="D222" s="7"/>
       <c r="E222" s="5"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A223" s="6"/>
-      <c r="B223" s="5"/>
-      <c r="C223" s="7"/>
+      <c r="A223" s="6">
+        <v>45510</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C223" s="7">
+        <v>3160940</v>
+      </c>
       <c r="D223" s="7"/>
       <c r="E223" s="5"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A224" s="6"/>
-      <c r="B224" s="5"/>
-      <c r="C224" s="7"/>
+      <c r="A224" s="6">
+        <v>45511</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C224" s="7">
+        <v>2918138</v>
+      </c>
       <c r="D224" s="7"/>
       <c r="E224" s="5"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A225" s="6"/>
-      <c r="B225" s="5"/>
-      <c r="C225" s="7"/>
+      <c r="A225" s="6">
+        <v>45512</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C225" s="7">
+        <v>2635992</v>
+      </c>
       <c r="D225" s="7"/>
       <c r="E225" s="5"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A226" s="6"/>
-      <c r="B226" s="5"/>
-      <c r="C226" s="7"/>
+      <c r="A226" s="6">
+        <v>45513</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C226" s="7">
+        <v>2762121</v>
+      </c>
       <c r="D226" s="7"/>
       <c r="E226" s="5"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A227" s="6"/>
-      <c r="B227" s="5"/>
-      <c r="C227" s="7"/>
+      <c r="A227" s="6">
+        <v>45514</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C227" s="7">
+        <v>11928161</v>
+      </c>
       <c r="D227" s="7"/>
       <c r="E227" s="5"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A228" s="6"/>
-      <c r="B228" s="5"/>
-      <c r="C228" s="7"/>
+      <c r="A228" s="6">
+        <v>45515</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C228" s="7">
+        <v>2529527</v>
+      </c>
       <c r="D228" s="7"/>
       <c r="E228" s="5"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A229" s="6"/>
-      <c r="B229" s="5"/>
-      <c r="C229" s="7"/>
+      <c r="A229" s="6">
+        <v>45516</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C229" s="7">
+        <v>1729029</v>
+      </c>
       <c r="D229" s="7"/>
       <c r="E229" s="5"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A230" s="6"/>
-      <c r="B230" s="5"/>
-      <c r="C230" s="7"/>
+      <c r="A230" s="6">
+        <v>45517</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C230" s="7">
+        <v>1560296</v>
+      </c>
       <c r="D230" s="7"/>
       <c r="E230" s="5"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A231" s="6"/>
-      <c r="B231" s="5"/>
-      <c r="C231" s="7"/>
+      <c r="A231" s="6">
+        <v>45518</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C231" s="7">
+        <v>1343811</v>
+      </c>
       <c r="D231" s="7"/>
       <c r="E231" s="5"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A232" s="6"/>
-      <c r="B232" s="5"/>
-      <c r="C232" s="7"/>
+      <c r="A232" s="6">
+        <v>45519</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C232" s="7">
+        <v>2958767</v>
+      </c>
       <c r="D232" s="7"/>
       <c r="E232" s="5"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A233" s="6"/>
-      <c r="B233" s="5"/>
-      <c r="C233" s="7"/>
+      <c r="A233" s="6">
+        <v>45520</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C233" s="7">
+        <v>1582693</v>
+      </c>
       <c r="D233" s="7"/>
       <c r="E233" s="5"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A234" s="6"/>
-      <c r="B234" s="5"/>
-      <c r="C234" s="7"/>
+      <c r="A234" s="6">
+        <v>45521</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C234" s="7">
+        <v>1679063</v>
+      </c>
       <c r="D234" s="7"/>
       <c r="E234" s="5"/>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A235" s="6"/>
-      <c r="B235" s="5"/>
-      <c r="C235" s="7"/>
+      <c r="A235" s="6">
+        <v>45522</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C235" s="7">
+        <v>4829006</v>
+      </c>
       <c r="D235" s="7"/>
       <c r="E235" s="5"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A236" s="6"/>
-      <c r="B236" s="5"/>
-      <c r="C236" s="7"/>
+      <c r="A236" s="6">
+        <v>45523</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C236" s="7">
+        <v>1522887</v>
+      </c>
       <c r="D236" s="7"/>
       <c r="E236" s="5"/>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A237" s="6"/>
-      <c r="B237" s="5"/>
-      <c r="C237" s="7"/>
+      <c r="A237" s="6">
+        <v>45524</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C237" s="7">
+        <v>3123140</v>
+      </c>
       <c r="D237" s="7"/>
       <c r="E237" s="5"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A238" s="6"/>
-      <c r="B238" s="5"/>
-      <c r="C238" s="7"/>
+      <c r="A238" s="6">
+        <v>45525</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C238" s="7">
+        <v>1594342</v>
+      </c>
       <c r="D238" s="7"/>
       <c r="E238" s="5"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A239" s="6"/>
-      <c r="B239" s="5"/>
-      <c r="C239" s="7"/>
+      <c r="A239" s="6">
+        <v>45526</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C239" s="7">
+        <v>1824745</v>
+      </c>
       <c r="D239" s="7"/>
       <c r="E239" s="5"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A240" s="6"/>
-      <c r="B240" s="5"/>
-      <c r="C240" s="7"/>
+      <c r="A240" s="6">
+        <v>45527</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C240" s="7">
+        <v>1073414</v>
+      </c>
       <c r="D240" s="7"/>
       <c r="E240" s="5"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A241" s="6"/>
-      <c r="B241" s="5"/>
-      <c r="C241" s="7"/>
+      <c r="A241" s="6">
+        <v>45528</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C241" s="7">
+        <v>2277664</v>
+      </c>
       <c r="D241" s="7"/>
       <c r="E241" s="5"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A242" s="6"/>
-      <c r="B242" s="5"/>
-      <c r="C242" s="7"/>
+      <c r="A242" s="6">
+        <v>45529</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C242" s="7">
+        <v>11999131</v>
+      </c>
       <c r="D242" s="7"/>
       <c r="E242" s="5"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A243" s="6"/>
-      <c r="B243" s="5"/>
-      <c r="C243" s="7"/>
+      <c r="A243" s="6">
+        <v>45530</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C243" s="7">
+        <v>4584959</v>
+      </c>
       <c r="D243" s="7"/>
       <c r="E243" s="5"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A244" s="6"/>
-      <c r="B244" s="5"/>
-      <c r="C244" s="7"/>
+      <c r="A244" s="6">
+        <v>45531</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C244" s="7">
+        <v>1886748</v>
+      </c>
       <c r="D244" s="7"/>
       <c r="E244" s="5"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A245" s="6"/>
-      <c r="B245" s="5"/>
-      <c r="C245" s="7"/>
+      <c r="A245" s="6">
+        <v>45532</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C245" s="7">
+        <v>1030961</v>
+      </c>
       <c r="D245" s="7"/>
       <c r="E245" s="5"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A246" s="6"/>
-      <c r="B246" s="5"/>
-      <c r="C246" s="7"/>
+      <c r="A246" s="6">
+        <v>45533</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C246" s="7">
+        <v>2000897</v>
+      </c>
       <c r="D246" s="7"/>
       <c r="E246" s="5"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A247" s="6"/>
-      <c r="B247" s="5"/>
-      <c r="C247" s="7"/>
+      <c r="A247" s="6">
+        <v>45534</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C247" s="7">
+        <v>1916770</v>
+      </c>
       <c r="D247" s="7"/>
       <c r="E247" s="5"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A248" s="6"/>
-      <c r="B248" s="5"/>
-      <c r="C248" s="7"/>
+      <c r="A248" s="6">
+        <v>45535</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C248" s="7">
+        <v>1037021</v>
+      </c>
       <c r="D248" s="7"/>
       <c r="E248" s="5"/>
     </row>
@@ -2853,219 +3787,405 @@
       <c r="E249" s="5"/>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A250" s="6"/>
-      <c r="B250" s="5"/>
-      <c r="C250" s="7"/>
+      <c r="A250" s="6">
+        <v>45139</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C250" s="7">
+        <v>5776048</v>
+      </c>
       <c r="D250" s="7"/>
       <c r="E250" s="5"/>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A251" s="6"/>
-      <c r="B251" s="5"/>
-      <c r="C251" s="7"/>
+      <c r="A251" s="6">
+        <v>45140</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C251" s="7">
+        <v>1827018</v>
+      </c>
       <c r="D251" s="7"/>
       <c r="E251" s="5"/>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A252" s="6"/>
-      <c r="B252" s="5"/>
-      <c r="C252" s="7"/>
+      <c r="A252" s="6">
+        <v>45141</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C252" s="7">
+        <v>1371602</v>
+      </c>
       <c r="D252" s="7"/>
       <c r="E252" s="5"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A253" s="6"/>
-      <c r="B253" s="5"/>
-      <c r="C253" s="7"/>
+      <c r="A253" s="6">
+        <v>45142</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C253" s="7">
+        <v>1254689</v>
+      </c>
       <c r="D253" s="7"/>
       <c r="E253" s="5"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A254" s="6"/>
-      <c r="B254" s="5"/>
-      <c r="C254" s="7"/>
+      <c r="A254" s="6">
+        <v>45143</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C254" s="7">
+        <v>13512157</v>
+      </c>
       <c r="D254" s="7"/>
       <c r="E254" s="5"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A255" s="6"/>
-      <c r="B255" s="5"/>
-      <c r="C255" s="7"/>
+      <c r="A255" s="6">
+        <v>45144</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C255" s="7">
+        <v>3616514</v>
+      </c>
       <c r="D255" s="7"/>
       <c r="E255" s="5"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A256" s="6"/>
-      <c r="B256" s="5"/>
-      <c r="C256" s="7"/>
+      <c r="A256" s="6">
+        <v>45145</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C256" s="7">
+        <v>2091446</v>
+      </c>
       <c r="D256" s="7"/>
       <c r="E256" s="5"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A257" s="6"/>
-      <c r="B257" s="5"/>
-      <c r="C257" s="7"/>
+      <c r="A257" s="6">
+        <v>45146</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C257" s="7">
+        <v>1534737</v>
+      </c>
       <c r="D257" s="7"/>
       <c r="E257" s="5"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A258" s="6"/>
-      <c r="B258" s="5"/>
-      <c r="C258" s="7"/>
+      <c r="A258" s="6">
+        <v>45147</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C258" s="7">
+        <v>1308472</v>
+      </c>
       <c r="D258" s="7"/>
       <c r="E258" s="5"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A259" s="6"/>
-      <c r="B259" s="5"/>
-      <c r="C259" s="7"/>
+      <c r="A259" s="6">
+        <v>45148</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C259" s="7">
+        <v>10811924</v>
+      </c>
       <c r="D259" s="7"/>
       <c r="E259" s="5"/>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A260" s="6"/>
-      <c r="B260" s="5"/>
-      <c r="C260" s="7"/>
+      <c r="A260" s="6">
+        <v>45149</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C260" s="7">
+        <v>1310227</v>
+      </c>
       <c r="D260" s="7"/>
       <c r="E260" s="5"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A261" s="6"/>
-      <c r="B261" s="5"/>
-      <c r="C261" s="7"/>
+      <c r="A261" s="6">
+        <v>45150</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C261" s="7">
+        <v>1017942</v>
+      </c>
       <c r="D261" s="7"/>
       <c r="E261" s="5"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A262" s="6"/>
-      <c r="B262" s="5"/>
-      <c r="C262" s="7"/>
+      <c r="A262" s="6">
+        <v>45151</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C262" s="7">
+        <v>1151998</v>
+      </c>
       <c r="D262" s="7"/>
       <c r="E262" s="5"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A263" s="6"/>
-      <c r="B263" s="5"/>
-      <c r="C263" s="7"/>
+      <c r="A263" s="6">
+        <v>45152</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C263" s="7">
+        <v>786601</v>
+      </c>
       <c r="D263" s="7"/>
       <c r="E263" s="5"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A264" s="6"/>
-      <c r="B264" s="5"/>
-      <c r="C264" s="7"/>
+      <c r="A264" s="6">
+        <v>45153</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C264" s="7">
+        <v>2465265</v>
+      </c>
       <c r="D264" s="7"/>
       <c r="E264" s="5"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A265" s="6"/>
-      <c r="B265" s="5"/>
-      <c r="C265" s="7"/>
+      <c r="A265" s="6">
+        <v>45154</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C265" s="7">
+        <v>1289658</v>
+      </c>
       <c r="D265" s="7"/>
       <c r="E265" s="5"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A266" s="6"/>
-      <c r="B266" s="5"/>
-      <c r="C266" s="7"/>
+      <c r="A266" s="6">
+        <v>45155</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C266" s="7">
+        <v>978370</v>
+      </c>
       <c r="D266" s="7"/>
       <c r="E266" s="5"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A267" s="6"/>
-      <c r="B267" s="5"/>
-      <c r="C267" s="7"/>
+      <c r="A267" s="6">
+        <v>45156</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C267" s="7">
+        <v>2743064</v>
+      </c>
       <c r="D267" s="7"/>
       <c r="E267" s="5"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A268" s="6"/>
-      <c r="B268" s="5"/>
-      <c r="C268" s="7"/>
+      <c r="A268" s="6">
+        <v>45157</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C268" s="7">
+        <v>863125</v>
+      </c>
       <c r="D268" s="7"/>
       <c r="E268" s="5"/>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A269" s="6"/>
-      <c r="B269" s="5"/>
-      <c r="C269" s="7"/>
+      <c r="A269" s="6">
+        <v>45158</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C269" s="7">
+        <v>3828711</v>
+      </c>
       <c r="D269" s="7"/>
       <c r="E269" s="5"/>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A270" s="6"/>
-      <c r="B270" s="5"/>
-      <c r="C270" s="7"/>
+      <c r="A270" s="6">
+        <v>45159</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C270" s="7">
+        <v>1108926</v>
+      </c>
       <c r="D270" s="7"/>
       <c r="E270" s="5"/>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A271" s="6"/>
-      <c r="B271" s="5"/>
-      <c r="C271" s="7"/>
+      <c r="A271" s="6">
+        <v>45160</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C271" s="7">
+        <v>1027198</v>
+      </c>
       <c r="D271" s="7"/>
       <c r="E271" s="5"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A272" s="6"/>
-      <c r="B272" s="5"/>
-      <c r="C272" s="7"/>
+      <c r="A272" s="6">
+        <v>45161</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C272" s="7">
+        <v>815762</v>
+      </c>
       <c r="D272" s="7"/>
       <c r="E272" s="5"/>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A273" s="6"/>
-      <c r="B273" s="5"/>
-      <c r="C273" s="7"/>
+      <c r="A273" s="6">
+        <v>45162</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C273" s="7">
+        <v>1238806</v>
+      </c>
       <c r="D273" s="7"/>
       <c r="E273" s="5"/>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A274" s="6"/>
-      <c r="B274" s="5"/>
-      <c r="C274" s="7"/>
+      <c r="A274" s="6">
+        <v>45163</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C274" s="7">
+        <v>11401148</v>
+      </c>
       <c r="D274" s="7"/>
       <c r="E274" s="5"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A275" s="6"/>
-      <c r="B275" s="5"/>
-      <c r="C275" s="7"/>
+      <c r="A275" s="6">
+        <v>45164</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C275" s="7">
+        <v>2744114</v>
+      </c>
       <c r="D275" s="7"/>
       <c r="E275" s="5"/>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A276" s="6"/>
-      <c r="B276" s="5"/>
-      <c r="C276" s="7"/>
+      <c r="A276" s="6">
+        <v>45165</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C276" s="7">
+        <v>1728787</v>
+      </c>
       <c r="D276" s="7"/>
       <c r="E276" s="5"/>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A277" s="6"/>
-      <c r="B277" s="5"/>
-      <c r="C277" s="7"/>
+      <c r="A277" s="6">
+        <v>45166</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C277" s="7">
+        <v>861613</v>
+      </c>
       <c r="D277" s="7"/>
       <c r="E277" s="5"/>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A278" s="6"/>
-      <c r="B278" s="5"/>
-      <c r="C278" s="7"/>
+      <c r="A278" s="6">
+        <v>45167</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C278" s="7">
+        <v>776720</v>
+      </c>
       <c r="D278" s="7"/>
       <c r="E278" s="5"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A279" s="6"/>
-      <c r="B279" s="5"/>
-      <c r="C279" s="7"/>
+      <c r="A279" s="6">
+        <v>45168</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C279" s="7">
+        <v>1887747</v>
+      </c>
       <c r="D279" s="7"/>
       <c r="E279" s="5"/>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A280" s="6"/>
-      <c r="B280" s="5"/>
-      <c r="C280" s="7"/>
+      <c r="A280" s="6">
+        <v>45169</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C280" s="7">
+        <v>1155282</v>
+      </c>
       <c r="D280" s="7"/>
       <c r="E280" s="5"/>
     </row>
@@ -6715,6 +7835,748 @@
       <c r="C801" s="7"/>
       <c r="D801" s="7"/>
       <c r="E801" s="5"/>
+    </row>
+    <row r="802" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A802" s="6"/>
+      <c r="B802" s="5"/>
+      <c r="C802" s="7"/>
+      <c r="D802" s="7"/>
+      <c r="E802" s="5"/>
+    </row>
+    <row r="803" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A803" s="6"/>
+      <c r="B803" s="5"/>
+      <c r="C803" s="7"/>
+      <c r="D803" s="7"/>
+      <c r="E803" s="5"/>
+    </row>
+    <row r="804" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A804" s="6"/>
+      <c r="B804" s="5"/>
+      <c r="C804" s="7"/>
+      <c r="D804" s="7"/>
+      <c r="E804" s="5"/>
+    </row>
+    <row r="805" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A805" s="6"/>
+      <c r="B805" s="5"/>
+      <c r="C805" s="7"/>
+      <c r="D805" s="7"/>
+      <c r="E805" s="5"/>
+    </row>
+    <row r="806" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A806" s="6"/>
+      <c r="B806" s="5"/>
+      <c r="C806" s="7"/>
+      <c r="D806" s="7"/>
+      <c r="E806" s="5"/>
+    </row>
+    <row r="807" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A807" s="6"/>
+      <c r="B807" s="5"/>
+      <c r="C807" s="7"/>
+      <c r="D807" s="7"/>
+      <c r="E807" s="5"/>
+    </row>
+    <row r="808" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A808" s="6"/>
+      <c r="B808" s="5"/>
+      <c r="C808" s="7"/>
+      <c r="D808" s="7"/>
+      <c r="E808" s="5"/>
+    </row>
+    <row r="809" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A809" s="6"/>
+      <c r="B809" s="5"/>
+      <c r="C809" s="7"/>
+      <c r="D809" s="7"/>
+      <c r="E809" s="5"/>
+    </row>
+    <row r="810" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A810" s="6"/>
+      <c r="B810" s="5"/>
+      <c r="C810" s="7"/>
+      <c r="D810" s="7"/>
+      <c r="E810" s="5"/>
+    </row>
+    <row r="811" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A811" s="6"/>
+      <c r="B811" s="5"/>
+      <c r="C811" s="7"/>
+      <c r="D811" s="7"/>
+      <c r="E811" s="5"/>
+    </row>
+    <row r="812" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A812" s="6"/>
+      <c r="B812" s="5"/>
+      <c r="C812" s="7"/>
+      <c r="D812" s="7"/>
+      <c r="E812" s="5"/>
+    </row>
+    <row r="813" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A813" s="6"/>
+      <c r="B813" s="5"/>
+      <c r="C813" s="7"/>
+      <c r="D813" s="7"/>
+      <c r="E813" s="5"/>
+    </row>
+    <row r="814" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A814" s="6"/>
+      <c r="B814" s="5"/>
+      <c r="C814" s="7"/>
+      <c r="D814" s="7"/>
+      <c r="E814" s="5"/>
+    </row>
+    <row r="815" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A815" s="6"/>
+      <c r="B815" s="5"/>
+      <c r="C815" s="7"/>
+      <c r="D815" s="7"/>
+      <c r="E815" s="5"/>
+    </row>
+    <row r="816" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A816" s="6"/>
+      <c r="B816" s="5"/>
+      <c r="C816" s="7"/>
+      <c r="D816" s="7"/>
+      <c r="E816" s="5"/>
+    </row>
+    <row r="817" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A817" s="6"/>
+      <c r="B817" s="5"/>
+      <c r="C817" s="7"/>
+      <c r="D817" s="7"/>
+      <c r="E817" s="5"/>
+    </row>
+    <row r="818" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A818" s="6"/>
+      <c r="B818" s="5"/>
+      <c r="C818" s="7"/>
+      <c r="D818" s="7"/>
+      <c r="E818" s="5"/>
+    </row>
+    <row r="819" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A819" s="6"/>
+      <c r="B819" s="5"/>
+      <c r="C819" s="7"/>
+      <c r="D819" s="7"/>
+      <c r="E819" s="5"/>
+    </row>
+    <row r="820" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A820" s="6"/>
+      <c r="B820" s="5"/>
+      <c r="C820" s="7"/>
+      <c r="D820" s="7"/>
+      <c r="E820" s="5"/>
+    </row>
+    <row r="821" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A821" s="6"/>
+      <c r="B821" s="5"/>
+      <c r="C821" s="7"/>
+      <c r="D821" s="7"/>
+      <c r="E821" s="5"/>
+    </row>
+    <row r="822" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A822" s="6"/>
+      <c r="B822" s="5"/>
+      <c r="C822" s="7"/>
+      <c r="D822" s="7"/>
+      <c r="E822" s="5"/>
+    </row>
+    <row r="823" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A823" s="6"/>
+      <c r="B823" s="5"/>
+      <c r="C823" s="7"/>
+      <c r="D823" s="7"/>
+      <c r="E823" s="5"/>
+    </row>
+    <row r="824" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A824" s="6"/>
+      <c r="B824" s="5"/>
+      <c r="C824" s="7"/>
+      <c r="D824" s="7"/>
+      <c r="E824" s="5"/>
+    </row>
+    <row r="825" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A825" s="6"/>
+      <c r="B825" s="5"/>
+      <c r="C825" s="7"/>
+      <c r="D825" s="7"/>
+      <c r="E825" s="5"/>
+    </row>
+    <row r="826" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A826" s="6"/>
+      <c r="B826" s="5"/>
+      <c r="C826" s="7"/>
+      <c r="D826" s="7"/>
+      <c r="E826" s="5"/>
+    </row>
+    <row r="827" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A827" s="6"/>
+      <c r="B827" s="5"/>
+      <c r="C827" s="7"/>
+      <c r="D827" s="7"/>
+      <c r="E827" s="5"/>
+    </row>
+    <row r="828" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A828" s="6"/>
+      <c r="B828" s="5"/>
+      <c r="C828" s="7"/>
+      <c r="D828" s="7"/>
+      <c r="E828" s="5"/>
+    </row>
+    <row r="829" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A829" s="6"/>
+      <c r="B829" s="5"/>
+      <c r="C829" s="7"/>
+      <c r="D829" s="7"/>
+      <c r="E829" s="5"/>
+    </row>
+    <row r="830" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A830" s="6"/>
+      <c r="B830" s="5"/>
+      <c r="C830" s="7"/>
+      <c r="D830" s="7"/>
+      <c r="E830" s="5"/>
+    </row>
+    <row r="831" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A831" s="6"/>
+      <c r="B831" s="5"/>
+      <c r="C831" s="7"/>
+      <c r="D831" s="7"/>
+      <c r="E831" s="5"/>
+    </row>
+    <row r="832" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A832" s="6"/>
+      <c r="B832" s="5"/>
+      <c r="C832" s="7"/>
+      <c r="D832" s="7"/>
+      <c r="E832" s="5"/>
+    </row>
+    <row r="833" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A833" s="6"/>
+      <c r="B833" s="5"/>
+      <c r="C833" s="7"/>
+      <c r="D833" s="7"/>
+      <c r="E833" s="5"/>
+    </row>
+    <row r="834" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A834" s="6"/>
+      <c r="B834" s="5"/>
+      <c r="C834" s="7"/>
+      <c r="D834" s="7"/>
+      <c r="E834" s="5"/>
+    </row>
+    <row r="835" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A835" s="6"/>
+      <c r="B835" s="5"/>
+      <c r="C835" s="7"/>
+      <c r="D835" s="7"/>
+      <c r="E835" s="5"/>
+    </row>
+    <row r="836" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A836" s="6"/>
+      <c r="B836" s="5"/>
+      <c r="C836" s="7"/>
+      <c r="D836" s="7"/>
+      <c r="E836" s="5"/>
+    </row>
+    <row r="837" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A837" s="6"/>
+      <c r="B837" s="5"/>
+      <c r="C837" s="7"/>
+      <c r="D837" s="7"/>
+      <c r="E837" s="5"/>
+    </row>
+    <row r="838" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A838" s="6"/>
+      <c r="B838" s="5"/>
+      <c r="C838" s="7"/>
+      <c r="D838" s="7"/>
+      <c r="E838" s="5"/>
+    </row>
+    <row r="839" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A839" s="6"/>
+      <c r="B839" s="5"/>
+      <c r="C839" s="7"/>
+      <c r="D839" s="7"/>
+      <c r="E839" s="5"/>
+    </row>
+    <row r="840" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A840" s="6"/>
+      <c r="B840" s="5"/>
+      <c r="C840" s="7"/>
+      <c r="D840" s="7"/>
+      <c r="E840" s="5"/>
+    </row>
+    <row r="841" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A841" s="6"/>
+      <c r="B841" s="5"/>
+      <c r="C841" s="7"/>
+      <c r="D841" s="7"/>
+      <c r="E841" s="5"/>
+    </row>
+    <row r="842" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A842" s="6"/>
+      <c r="B842" s="5"/>
+      <c r="C842" s="7"/>
+      <c r="D842" s="7"/>
+      <c r="E842" s="5"/>
+    </row>
+    <row r="843" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A843" s="6"/>
+      <c r="B843" s="5"/>
+      <c r="C843" s="7"/>
+      <c r="D843" s="7"/>
+      <c r="E843" s="5"/>
+    </row>
+    <row r="844" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A844" s="6"/>
+      <c r="B844" s="5"/>
+      <c r="C844" s="7"/>
+      <c r="D844" s="7"/>
+      <c r="E844" s="5"/>
+    </row>
+    <row r="845" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A845" s="6"/>
+      <c r="B845" s="5"/>
+      <c r="C845" s="7"/>
+      <c r="D845" s="7"/>
+      <c r="E845" s="5"/>
+    </row>
+    <row r="846" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A846" s="6"/>
+      <c r="B846" s="5"/>
+      <c r="C846" s="7"/>
+      <c r="D846" s="7"/>
+      <c r="E846" s="5"/>
+    </row>
+    <row r="847" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A847" s="6"/>
+      <c r="B847" s="5"/>
+      <c r="C847" s="7"/>
+      <c r="D847" s="7"/>
+      <c r="E847" s="5"/>
+    </row>
+    <row r="848" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A848" s="6"/>
+      <c r="B848" s="5"/>
+      <c r="C848" s="7"/>
+      <c r="D848" s="7"/>
+      <c r="E848" s="5"/>
+    </row>
+    <row r="849" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A849" s="6"/>
+      <c r="B849" s="5"/>
+      <c r="C849" s="7"/>
+      <c r="D849" s="7"/>
+      <c r="E849" s="5"/>
+    </row>
+    <row r="850" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A850" s="6"/>
+      <c r="B850" s="5"/>
+      <c r="C850" s="7"/>
+      <c r="D850" s="7"/>
+      <c r="E850" s="5"/>
+    </row>
+    <row r="851" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A851" s="6"/>
+      <c r="B851" s="5"/>
+      <c r="C851" s="7"/>
+      <c r="D851" s="7"/>
+      <c r="E851" s="5"/>
+    </row>
+    <row r="852" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A852" s="6"/>
+      <c r="B852" s="5"/>
+      <c r="C852" s="7"/>
+      <c r="D852" s="7"/>
+      <c r="E852" s="5"/>
+    </row>
+    <row r="853" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A853" s="6"/>
+      <c r="B853" s="5"/>
+      <c r="C853" s="7"/>
+      <c r="D853" s="7"/>
+      <c r="E853" s="5"/>
+    </row>
+    <row r="854" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A854" s="6"/>
+      <c r="B854" s="5"/>
+      <c r="C854" s="7"/>
+      <c r="D854" s="7"/>
+      <c r="E854" s="5"/>
+    </row>
+    <row r="855" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A855" s="6"/>
+      <c r="B855" s="5"/>
+      <c r="C855" s="7"/>
+      <c r="D855" s="7"/>
+      <c r="E855" s="5"/>
+    </row>
+    <row r="856" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A856" s="6"/>
+      <c r="B856" s="5"/>
+      <c r="C856" s="7"/>
+      <c r="D856" s="7"/>
+      <c r="E856" s="5"/>
+    </row>
+    <row r="857" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A857" s="6"/>
+      <c r="B857" s="5"/>
+      <c r="C857" s="7"/>
+      <c r="D857" s="7"/>
+      <c r="E857" s="5"/>
+    </row>
+    <row r="858" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A858" s="6"/>
+      <c r="B858" s="5"/>
+      <c r="C858" s="7"/>
+      <c r="D858" s="7"/>
+      <c r="E858" s="5"/>
+    </row>
+    <row r="859" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A859" s="6"/>
+      <c r="B859" s="5"/>
+      <c r="C859" s="7"/>
+      <c r="D859" s="7"/>
+      <c r="E859" s="5"/>
+    </row>
+    <row r="860" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A860" s="6"/>
+      <c r="B860" s="5"/>
+      <c r="C860" s="7"/>
+      <c r="D860" s="7"/>
+      <c r="E860" s="5"/>
+    </row>
+    <row r="861" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A861" s="6"/>
+      <c r="B861" s="5"/>
+      <c r="C861" s="7"/>
+      <c r="D861" s="7"/>
+      <c r="E861" s="5"/>
+    </row>
+    <row r="862" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A862" s="6"/>
+      <c r="B862" s="5"/>
+      <c r="C862" s="7"/>
+      <c r="D862" s="7"/>
+      <c r="E862" s="5"/>
+    </row>
+    <row r="863" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A863" s="6"/>
+      <c r="B863" s="5"/>
+      <c r="C863" s="7"/>
+      <c r="D863" s="7"/>
+      <c r="E863" s="5"/>
+    </row>
+    <row r="864" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A864" s="6"/>
+      <c r="B864" s="5"/>
+      <c r="C864" s="7"/>
+      <c r="D864" s="7"/>
+      <c r="E864" s="5"/>
+    </row>
+    <row r="865" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A865" s="6"/>
+      <c r="B865" s="5"/>
+      <c r="C865" s="7"/>
+      <c r="D865" s="7"/>
+      <c r="E865" s="5"/>
+    </row>
+    <row r="866" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A866" s="6"/>
+      <c r="B866" s="5"/>
+      <c r="C866" s="7"/>
+      <c r="D866" s="7"/>
+      <c r="E866" s="5"/>
+    </row>
+    <row r="867" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A867" s="6"/>
+      <c r="B867" s="5"/>
+      <c r="C867" s="7"/>
+      <c r="D867" s="7"/>
+      <c r="E867" s="5"/>
+    </row>
+    <row r="868" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A868" s="6"/>
+      <c r="B868" s="5"/>
+      <c r="C868" s="7"/>
+      <c r="D868" s="7"/>
+      <c r="E868" s="5"/>
+    </row>
+    <row r="869" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A869" s="6"/>
+      <c r="B869" s="5"/>
+      <c r="C869" s="7"/>
+      <c r="D869" s="7"/>
+      <c r="E869" s="5"/>
+    </row>
+    <row r="870" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A870" s="6"/>
+      <c r="B870" s="5"/>
+      <c r="C870" s="7"/>
+      <c r="D870" s="7"/>
+      <c r="E870" s="5"/>
+    </row>
+    <row r="871" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A871" s="6"/>
+      <c r="B871" s="5"/>
+      <c r="C871" s="7"/>
+      <c r="D871" s="7"/>
+      <c r="E871" s="5"/>
+    </row>
+    <row r="872" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A872" s="6"/>
+      <c r="B872" s="5"/>
+      <c r="C872" s="7"/>
+      <c r="D872" s="7"/>
+      <c r="E872" s="5"/>
+    </row>
+    <row r="873" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A873" s="6"/>
+      <c r="B873" s="5"/>
+      <c r="C873" s="7"/>
+      <c r="D873" s="7"/>
+      <c r="E873" s="5"/>
+    </row>
+    <row r="874" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A874" s="6"/>
+      <c r="B874" s="5"/>
+      <c r="C874" s="7"/>
+      <c r="D874" s="7"/>
+      <c r="E874" s="5"/>
+    </row>
+    <row r="875" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A875" s="6"/>
+      <c r="B875" s="5"/>
+      <c r="C875" s="7"/>
+      <c r="D875" s="7"/>
+      <c r="E875" s="5"/>
+    </row>
+    <row r="876" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A876" s="6"/>
+      <c r="B876" s="5"/>
+      <c r="C876" s="7"/>
+      <c r="D876" s="7"/>
+      <c r="E876" s="5"/>
+    </row>
+    <row r="877" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A877" s="6"/>
+      <c r="B877" s="5"/>
+      <c r="C877" s="7"/>
+      <c r="D877" s="7"/>
+      <c r="E877" s="5"/>
+    </row>
+    <row r="878" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A878" s="6"/>
+      <c r="B878" s="5"/>
+      <c r="C878" s="7"/>
+      <c r="D878" s="7"/>
+      <c r="E878" s="5"/>
+    </row>
+    <row r="879" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A879" s="6"/>
+      <c r="B879" s="5"/>
+      <c r="C879" s="7"/>
+      <c r="D879" s="7"/>
+      <c r="E879" s="5"/>
+    </row>
+    <row r="880" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A880" s="6"/>
+      <c r="B880" s="5"/>
+      <c r="C880" s="7"/>
+      <c r="D880" s="7"/>
+      <c r="E880" s="5"/>
+    </row>
+    <row r="881" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A881" s="6"/>
+      <c r="B881" s="5"/>
+      <c r="C881" s="7"/>
+      <c r="D881" s="7"/>
+      <c r="E881" s="5"/>
+    </row>
+    <row r="882" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A882" s="6"/>
+      <c r="B882" s="5"/>
+      <c r="C882" s="7"/>
+      <c r="D882" s="7"/>
+      <c r="E882" s="5"/>
+    </row>
+    <row r="883" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A883" s="6"/>
+      <c r="B883" s="5"/>
+      <c r="C883" s="7"/>
+      <c r="D883" s="7"/>
+      <c r="E883" s="5"/>
+    </row>
+    <row r="884" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A884" s="6"/>
+      <c r="B884" s="5"/>
+      <c r="C884" s="7"/>
+      <c r="D884" s="7"/>
+      <c r="E884" s="5"/>
+    </row>
+    <row r="885" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A885" s="6"/>
+      <c r="B885" s="5"/>
+      <c r="C885" s="7"/>
+      <c r="D885" s="7"/>
+      <c r="E885" s="5"/>
+    </row>
+    <row r="886" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A886" s="6"/>
+      <c r="B886" s="5"/>
+      <c r="C886" s="7"/>
+      <c r="D886" s="7"/>
+      <c r="E886" s="5"/>
+    </row>
+    <row r="887" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A887" s="6"/>
+      <c r="B887" s="5"/>
+      <c r="C887" s="7"/>
+      <c r="D887" s="7"/>
+      <c r="E887" s="5"/>
+    </row>
+    <row r="888" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A888" s="6"/>
+      <c r="B888" s="5"/>
+      <c r="C888" s="7"/>
+      <c r="D888" s="7"/>
+      <c r="E888" s="5"/>
+    </row>
+    <row r="889" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A889" s="6"/>
+      <c r="B889" s="5"/>
+      <c r="C889" s="7"/>
+      <c r="D889" s="7"/>
+      <c r="E889" s="5"/>
+    </row>
+    <row r="890" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A890" s="6"/>
+      <c r="B890" s="5"/>
+      <c r="C890" s="7"/>
+      <c r="D890" s="7"/>
+      <c r="E890" s="5"/>
+    </row>
+    <row r="891" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A891" s="6"/>
+      <c r="B891" s="5"/>
+      <c r="C891" s="7"/>
+      <c r="D891" s="7"/>
+      <c r="E891" s="5"/>
+    </row>
+    <row r="892" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A892" s="6"/>
+      <c r="B892" s="5"/>
+      <c r="C892" s="7"/>
+      <c r="D892" s="7"/>
+      <c r="E892" s="5"/>
+    </row>
+    <row r="893" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A893" s="6"/>
+      <c r="B893" s="5"/>
+      <c r="C893" s="7"/>
+      <c r="D893" s="7"/>
+      <c r="E893" s="5"/>
+    </row>
+    <row r="894" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A894" s="6"/>
+      <c r="B894" s="5"/>
+      <c r="C894" s="7"/>
+      <c r="D894" s="7"/>
+      <c r="E894" s="5"/>
+    </row>
+    <row r="895" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A895" s="6"/>
+      <c r="B895" s="5"/>
+      <c r="C895" s="7"/>
+      <c r="D895" s="7"/>
+      <c r="E895" s="5"/>
+    </row>
+    <row r="896" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A896" s="6"/>
+      <c r="B896" s="5"/>
+      <c r="C896" s="7"/>
+      <c r="D896" s="7"/>
+      <c r="E896" s="5"/>
+    </row>
+    <row r="897" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A897" s="6"/>
+      <c r="B897" s="5"/>
+      <c r="C897" s="7"/>
+      <c r="D897" s="7"/>
+      <c r="E897" s="5"/>
+    </row>
+    <row r="898" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A898" s="6"/>
+      <c r="B898" s="5"/>
+      <c r="C898" s="7"/>
+      <c r="D898" s="7"/>
+      <c r="E898" s="5"/>
+    </row>
+    <row r="899" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A899" s="6"/>
+      <c r="B899" s="5"/>
+      <c r="C899" s="7"/>
+      <c r="D899" s="7"/>
+      <c r="E899" s="5"/>
+    </row>
+    <row r="900" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A900" s="6"/>
+      <c r="B900" s="5"/>
+      <c r="C900" s="7"/>
+      <c r="D900" s="7"/>
+      <c r="E900" s="5"/>
+    </row>
+    <row r="901" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A901" s="6"/>
+      <c r="B901" s="5"/>
+      <c r="C901" s="7"/>
+      <c r="D901" s="7"/>
+      <c r="E901" s="5"/>
+    </row>
+    <row r="902" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A902" s="6"/>
+      <c r="B902" s="5"/>
+      <c r="C902" s="7"/>
+      <c r="D902" s="7"/>
+      <c r="E902" s="5"/>
+    </row>
+    <row r="903" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A903" s="6"/>
+      <c r="B903" s="5"/>
+      <c r="C903" s="7"/>
+      <c r="D903" s="7"/>
+      <c r="E903" s="5"/>
+    </row>
+    <row r="904" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A904" s="6"/>
+      <c r="B904" s="5"/>
+      <c r="C904" s="7"/>
+      <c r="D904" s="7"/>
+      <c r="E904" s="5"/>
+    </row>
+    <row r="905" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A905" s="6"/>
+      <c r="B905" s="5"/>
+      <c r="C905" s="7"/>
+      <c r="D905" s="7"/>
+      <c r="E905" s="5"/>
+    </row>
+    <row r="906" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A906" s="6"/>
+      <c r="B906" s="5"/>
+      <c r="C906" s="7"/>
+      <c r="D906" s="7"/>
+      <c r="E906" s="5"/>
+    </row>
+    <row r="907" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A907" s="6"/>
+      <c r="B907" s="5"/>
+      <c r="C907" s="7"/>
+      <c r="D907" s="7"/>
+      <c r="E907" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5"/>
@@ -6726,7 +8588,7 @@
           <x14:formula1>
             <xm:f>店舗マスタ!$A$2:$A$31</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B801</xm:sqref>
+          <xm:sqref>B154:B907 B2:B139</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1721</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,8 +165,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -203,30 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -234,16 +210,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,6 +223,21 @@
       <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -271,9 +255,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,38 +293,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,16 +316,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +428,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,115 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,74 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -605,76 +668,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1722"/>
+  <dimension ref="A1:E1723"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23256,8 +23256,19 @@
         <v>1512486</v>
       </c>
     </row>
+    <row r="1723" spans="1:3">
+      <c r="A1723" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1723">
+        <v>6170410</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1721">
+  <autoFilter ref="A1:E1722">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,30 +204,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,21 +241,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,9 +255,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,14 +271,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -302,7 +279,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,8 +301,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -331,6 +317,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,9 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,109 +380,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +404,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,13 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,20 +595,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,19 +628,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +657,178 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1723"/>
+  <dimension ref="A1:E1724"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23267,8 +23267,19 @@
         <v>6170410</v>
       </c>
     </row>
+    <row r="1724" spans="1:3">
+      <c r="A1724" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1724">
+        <v>2322291</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1722">
+  <autoFilter ref="A1:E1723">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,10 +203,11 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -232,39 +233,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,7 +242,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,35 +255,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -332,9 +277,64 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,169 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -537,6 +375,168 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,7 +575,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,50 +595,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,6 +619,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -668,167 +644,191 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1724"/>
+  <dimension ref="A1:E1725"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23278,8 +23278,19 @@
         <v>2322291</v>
       </c>
     </row>
+    <row r="1725" spans="1:3">
+      <c r="A1725" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1725">
+        <v>13709822</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1723">
+  <autoFilter ref="A1:E1724">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,6 +205,105 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -227,36 +326,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,77 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,6 +362,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,49 +386,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,43 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +446,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +464,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,6 +619,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -615,21 +645,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,22 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1725"/>
+  <dimension ref="A1:E1726"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23289,8 +23289,19 @@
         <v>13709822</v>
       </c>
     </row>
+    <row r="1726" spans="1:3">
+      <c r="A1726" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1726">
+        <v>3256152</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1724">
+  <autoFilter ref="A1:E1725">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -203,29 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -233,24 +210,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,38 +226,38 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,11 +271,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -326,22 +310,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +398,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,25 +458,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,31 +488,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,25 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -590,22 +605,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,8 +613,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -651,20 +651,20 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1726"/>
+  <dimension ref="A1:E1727"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23300,8 +23300,19 @@
         <v>3256152</v>
       </c>
     </row>
+    <row r="1727" spans="1:3">
+      <c r="A1727" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1727">
+        <v>1851732</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1725">
+  <autoFilter ref="A1:E1726">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,30 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,20 +213,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,25 +228,38 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -299,6 +275,14 @@
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -324,8 +308,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -333,10 +333,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,79 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +416,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,49 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,18 +543,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -582,6 +597,50 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -605,65 +664,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1727"/>
+  <dimension ref="A1:E1728"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23311,8 +23311,19 @@
         <v>1851732</v>
       </c>
     </row>
+    <row r="1728" spans="1:3">
+      <c r="A1728" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1728">
+        <v>2967259</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1726">
+  <autoFilter ref="A1:E1727">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,15 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,6 +213,58 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,28 +280,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,7 +303,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,28 +325,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -308,32 +332,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,13 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +422,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,13 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +470,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,13 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,21 +572,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -597,6 +582,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,24 +630,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -660,11 +645,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1728"/>
+  <dimension ref="A1:E1729"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23322,8 +23322,19 @@
         <v>2967259</v>
       </c>
     </row>
+    <row r="1729" spans="1:3">
+      <c r="A1729" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1729">
+        <v>1765486</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1727">
+  <autoFilter ref="A1:E1728">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,16 +203,31 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,54 +240,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,15 +272,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,9 +280,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,15 +308,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -334,6 +318,22 @@
     <font>
       <b/>
       <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +404,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,19 +470,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,13 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,31 +586,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,6 +616,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -645,17 +651,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1729"/>
+  <dimension ref="A1:E1730"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23333,8 +23333,19 @@
         <v>1765486</v>
       </c>
     </row>
+    <row r="1730" spans="1:3">
+      <c r="A1730" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1730">
+        <v>4267820</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1728">
+  <autoFilter ref="A1:E1729">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,6 +203,21 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -211,15 +226,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,93 +257,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +274,74 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,25 +380,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,13 +410,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,61 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,13 +488,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,13 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,52 +586,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,8 +612,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -668,154 +629,193 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1730"/>
+  <dimension ref="A1:E1731"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23344,8 +23344,19 @@
         <v>4267820</v>
       </c>
     </row>
+    <row r="1731" spans="1:3">
+      <c r="A1731" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1731">
+        <v>1572919</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1729">
+  <autoFilter ref="A1:E1730">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,9 +210,69 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,40 +286,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,23 +308,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,37 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,7 +368,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,55 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +416,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,85 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -588,34 +588,34 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -639,6 +639,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -653,34 +668,19 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1731"/>
+  <dimension ref="A1:E1732"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23355,8 +23355,19 @@
         <v>1572919</v>
       </c>
     </row>
+    <row r="1732" spans="1:3">
+      <c r="A1732" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1732">
+        <v>1843808</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1730">
+  <autoFilter ref="A1:E1731">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,76 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,6 +220,57 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -294,7 +278,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -326,14 +310,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -341,7 +333,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,25 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,19 +416,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,13 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,31 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,17 +586,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -617,15 +606,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,6 +634,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1732"/>
+  <dimension ref="A1:E1733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23366,8 +23366,19 @@
         <v>1843808</v>
       </c>
     </row>
+    <row r="1733" spans="1:3">
+      <c r="A1733" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1733">
+        <v>1549067</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1731">
+  <autoFilter ref="A1:E1732">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,13 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -211,16 +218,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,16 +246,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,9 +276,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,23 +292,32 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,15 +332,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -326,22 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +386,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,13 +440,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,31 +470,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,19 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,19 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,7 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,6 +586,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -601,11 +621,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,8 +639,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,60 +668,25 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,140 +695,140 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1733"/>
+  <dimension ref="A1:E1734"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23377,8 +23377,19 @@
         <v>1549067</v>
       </c>
     </row>
+    <row r="1734" spans="1:3">
+      <c r="A1734" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1734">
+        <v>1938220</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1732">
+  <autoFilter ref="A1:E1733">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1734</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,8 +165,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -210,25 +210,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -246,9 +240,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,30 +271,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,33 +287,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,9 +302,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +404,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +440,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +464,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +488,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,97 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,6 +597,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,8 +639,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,50 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1734"/>
+  <dimension ref="A1:E1735"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23388,8 +23388,16 @@
         <v>1938220</v>
       </c>
     </row>
+    <row r="1735" spans="1:2">
+      <c r="A1735" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1733">
+  <autoFilter ref="A1:E1734">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,11 +203,17 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -220,37 +226,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,23 +239,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,14 +250,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,7 +272,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,9 +293,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +380,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +416,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,121 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -595,6 +595,56 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -618,63 +668,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1737"/>
+  <dimension ref="A1:E1738"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23421,8 +23421,19 @@
         <v>894407</v>
       </c>
     </row>
+    <row r="1738" spans="1:3">
+      <c r="A1738" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1738">
+        <v>1104033</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1736">
+  <autoFilter ref="A1:E1737">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,17 +203,34 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -232,13 +249,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -247,9 +257,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,60 +296,14 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,14 +319,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,61 +464,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,37 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,43 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,7 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,6 +634,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -635,46 +668,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1738"/>
+  <dimension ref="A1:E1739"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23432,8 +23432,19 @@
         <v>1104033</v>
       </c>
     </row>
+    <row r="1739" spans="1:3">
+      <c r="A1739" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1739">
+        <v>2135506</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1737">
+  <autoFilter ref="A1:E1738">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -203,14 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -218,99 +210,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -332,6 +233,89 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -340,8 +324,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +380,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +446,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,25 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,43 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,43 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,26 +571,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,6 +630,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -633,189 +668,154 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1739"/>
+  <dimension ref="A1:E1740"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23443,8 +23443,19 @@
         <v>2135506</v>
       </c>
     </row>
+    <row r="1740" spans="1:3">
+      <c r="A1740" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1740">
+        <v>9907540</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1738">
+  <autoFilter ref="A1:E1739">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,18 +203,43 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -226,8 +251,59 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,37 +317,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,47 +333,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -335,13 +342,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +428,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,25 +464,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,25 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,61 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -582,6 +582,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -602,15 +626,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,21 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1740"/>
+  <dimension ref="A1:E1741"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23454,8 +23454,19 @@
         <v>9907540</v>
       </c>
     </row>
+    <row r="1741" spans="1:3">
+      <c r="A1741" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1741">
+        <v>2358911</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1739">
+  <autoFilter ref="A1:E1740">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,6 +205,36 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -227,9 +257,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,38 +272,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,14 +288,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,14 +308,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -325,15 +316,24 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +404,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,31 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,109 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +513,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,9 +573,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -585,6 +587,30 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,17 +630,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -626,21 +641,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1741"/>
+  <dimension ref="A1:E1742"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23465,8 +23465,19 @@
         <v>2358911</v>
       </c>
     </row>
+    <row r="1742" spans="1:3">
+      <c r="A1742" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1742">
+        <v>2168340</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1740">
+  <autoFilter ref="A1:E1741">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,15 +204,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -233,8 +225,91 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -251,75 +326,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -331,17 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,7 +368,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,31 +404,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,67 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,31 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,26 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -602,30 +582,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,6 +610,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1742"/>
+  <dimension ref="A1:E1743"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23476,8 +23476,19 @@
         <v>2168340</v>
       </c>
     </row>
+    <row r="1743" spans="1:3">
+      <c r="A1743" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1743">
+        <v>2093630</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1741">
+  <autoFilter ref="A1:E1742">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,16 +203,23 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,16 +232,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,46 +271,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -309,6 +295,29 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -316,17 +325,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,14 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,175 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,6 +606,41 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,67 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1743"/>
+  <dimension ref="A1:E1744"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23487,8 +23487,19 @@
         <v>2093630</v>
       </c>
     </row>
+    <row r="1744" spans="1:3">
+      <c r="A1744" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1744">
+        <v>1078749</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1742">
+  <autoFilter ref="A1:E1743">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,38 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,13 +226,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -271,7 +248,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -279,23 +264,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -311,22 +280,53 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,43 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,13 +470,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,55 +500,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +537,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,30 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -612,35 +588,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,121 +618,171 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -791,44 +791,44 @@
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1744"/>
+  <dimension ref="A1:E1745"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23498,8 +23498,19 @@
         <v>1078749</v>
       </c>
     </row>
+    <row r="1745" spans="1:3">
+      <c r="A1745" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1745">
+        <v>2860749</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1743">
+  <autoFilter ref="A1:E1744">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,8 +165,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -203,6 +203,20 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -212,21 +226,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,16 +263,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -279,8 +293,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,16 +308,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,26 +324,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +374,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +428,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,133 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,30 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,12 +604,25 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -650,6 +639,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1745"/>
+  <dimension ref="A1:E1746"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23509,8 +23509,19 @@
         <v>2860749</v>
       </c>
     </row>
+    <row r="1746" spans="1:3">
+      <c r="A1746" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1746">
+        <v>1252579</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1744">
+  <autoFilter ref="A1:E1745">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,20 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -226,15 +212,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,36 +240,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -293,16 +248,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,6 +270,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -324,10 +293,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -342,6 +328,20 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +380,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +452,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,151 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,35 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,11 +595,37 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,10 +647,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1746"/>
+  <dimension ref="A1:E1747"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23520,8 +23520,19 @@
         <v>1252579</v>
       </c>
     </row>
+    <row r="1747" spans="1:3">
+      <c r="A1747" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1747">
+        <v>1013321</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1745">
+  <autoFilter ref="A1:E1746">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,23 @@
       <charset val="128"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -212,7 +227,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,9 +248,55 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,54 +316,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,39 +332,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,7 +368,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,169 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -591,6 +582,59 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,26 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -644,191 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1747"/>
+  <dimension ref="A1:E1748"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23531,8 +23531,19 @@
         <v>1013321</v>
       </c>
     </row>
+    <row r="1748" spans="1:3">
+      <c r="A1748" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1748">
+        <v>1013321</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1746">
+  <autoFilter ref="A1:E1747">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,16 +203,107 @@
       <charset val="128"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,68 +318,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -300,31 +332,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -332,16 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +422,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,25 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,85 +518,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,6 +586,62 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -606,65 +662,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1748"/>
+  <dimension ref="A1:E1749"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23542,8 +23542,19 @@
         <v>1013321</v>
       </c>
     </row>
+    <row r="1749" spans="1:3">
+      <c r="A1749" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1749">
+        <v>1091222</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1747">
+  <autoFilter ref="A1:E1748">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,60 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,8 +227,60 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -293,17 +294,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,31 +317,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,43 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,31 +434,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,19 +470,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,13 +488,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,13 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,7 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -597,32 +608,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,8 +639,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +648,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1749"/>
+  <dimension ref="A1:E1750"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23553,8 +23553,19 @@
         <v>1091222</v>
       </c>
     </row>
+    <row r="1750" spans="1:3">
+      <c r="A1750" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1750">
+        <v>1488536</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1748">
+  <autoFilter ref="A1:E1749">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,6 +204,36 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -211,9 +241,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,8 +271,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,12 +289,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -256,23 +303,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -280,7 +312,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -295,46 +327,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +386,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,25 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +488,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,61 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,11 +573,48 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,63 +635,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -668,154 +648,174 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1750"/>
+  <dimension ref="A1:E1751"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23564,8 +23564,19 @@
         <v>1488536</v>
       </c>
     </row>
+    <row r="1751" spans="1:3">
+      <c r="A1751" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1751">
+        <v>9045181</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1749">
+  <autoFilter ref="A1:E1750">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,31 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -219,28 +242,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -250,7 +251,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,9 +272,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,30 +311,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -320,7 +318,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,15 +331,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,25 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +386,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,25 +428,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,19 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,9 +573,74 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -603,232 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1751"/>
+  <dimension ref="A1:E1752"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23575,8 +23575,19 @@
         <v>9045181</v>
       </c>
     </row>
+    <row r="1752" spans="1:3">
+      <c r="A1752" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1752">
+        <v>1839914</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1750">
+  <autoFilter ref="A1:E1751">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,52 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -258,10 +212,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -279,8 +233,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,13 +296,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,9 +311,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -324,24 +324,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,18 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -386,7 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +392,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,127 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,13 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,17 +595,50 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -623,48 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,140 +695,140 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1752"/>
+  <dimension ref="A1:E1754"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23586,8 +23586,30 @@
         <v>1839914</v>
       </c>
     </row>
+    <row r="1753" spans="1:3">
+      <c r="A1753" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1753">
+        <v>1839914</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:3">
+      <c r="A1754" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1754">
+        <v>1655591</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1751">
+  <autoFilter ref="A1:E1753">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,28 +205,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -242,17 +220,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -264,8 +241,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,9 +277,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,9 +293,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,31 +308,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +380,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,31 +410,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,31 +452,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,35 +591,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,13 +636,35 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1754"/>
+  <dimension ref="A1:E1755"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23608,8 +23608,19 @@
         <v>1655591</v>
       </c>
     </row>
+    <row r="1755" spans="1:3">
+      <c r="A1755" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1755">
+        <v>5073910</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1753">
+  <autoFilter ref="A1:E1754">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,106 +205,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -325,14 +236,103 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -341,7 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +416,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,25 +470,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,25 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,13 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -587,6 +591,30 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,17 +634,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -635,200 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1755"/>
+  <dimension ref="A1:E1756"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23619,8 +23619,19 @@
         <v>5073910</v>
       </c>
     </row>
+    <row r="1756" spans="1:3">
+      <c r="A1756" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1756">
+        <v>2023656</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1754">
+  <autoFilter ref="A1:E1755">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -219,14 +219,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -235,15 +227,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,6 +245,20 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,50 +279,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -325,7 +288,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +321,27 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,7 +368,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,13 +464,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,55 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -595,26 +595,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,20 +623,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +659,176 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1756"/>
+  <dimension ref="A1:E1757"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23630,8 +23630,19 @@
         <v>2023656</v>
       </c>
     </row>
+    <row r="1757" spans="1:3">
+      <c r="A1757" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1757">
+        <v>3747643</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1755">
+  <autoFilter ref="A1:E1756">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -205,7 +205,45 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,11 +265,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -242,23 +287,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,32 +319,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,38 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,7 +368,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +386,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +500,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,73 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -586,22 +597,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,7 +631,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,26 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1757"/>
+  <dimension ref="A1:E1758"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23641,8 +23641,19 @@
         <v>3747643</v>
       </c>
     </row>
+    <row r="1758" spans="1:3">
+      <c r="A1758" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1758">
+        <v>1410826</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1756">
+  <autoFilter ref="A1:E1757">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -203,6 +203,82 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,7 +289,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,107 +333,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,37 +422,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,25 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,13 +482,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,11 +573,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,17 +595,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,17 +622,34 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,31 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,140 +695,140 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1758"/>
+  <dimension ref="A1:E1759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23652,8 +23652,19 @@
         <v>1410826</v>
       </c>
     </row>
+    <row r="1759" spans="1:3">
+      <c r="A1759" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1759">
+        <v>1482628</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1757">
+  <autoFilter ref="A1:E1758">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,20 +204,49 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -233,8 +262,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -249,39 +332,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,59 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,127 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +380,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +416,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,13 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,30 +615,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -630,11 +623,33 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,182 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1759"/>
+  <dimension ref="A1:E1760"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23663,8 +23663,19 @@
         <v>1482628</v>
       </c>
     </row>
+    <row r="1760" spans="1:3">
+      <c r="A1760" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1760">
+        <v>1076356</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1758">
+  <autoFilter ref="A1:E1759">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,24 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,7 +234,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,21 +265,52 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,30 +326,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,55 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,37 +488,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,127 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -586,17 +595,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -608,24 +606,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,8 +628,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,154 +648,174 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1760"/>
+  <dimension ref="A1:E1762"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23674,8 +23674,30 @@
         <v>1076356</v>
       </c>
     </row>
+    <row r="1761" spans="1:3">
+      <c r="A1761" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1761">
+        <v>1076356</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:3">
+      <c r="A1762" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1762">
+        <v>1544940</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1759">
+  <autoFilter ref="A1:E1761">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,38 +203,15 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,9 +232,54 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,8 +293,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,8 +309,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,6 +319,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,41 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,43 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,19 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,19 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,43 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,19 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,30 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -625,15 +601,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -645,6 +612,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +655,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1762"/>
+  <dimension ref="A1:E1763"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23696,8 +23696,19 @@
         <v>1544940</v>
       </c>
     </row>
+    <row r="1763" spans="1:3">
+      <c r="A1763" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1763">
+        <v>9490660</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1761">
+  <autoFilter ref="A1:E1762">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,8 +210,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,51 +241,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,6 +263,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -295,37 +295,37 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,11 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,31 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,73 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,47 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,8 +598,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -655,16 +634,37 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,115 +674,115 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -791,31 +791,31 @@
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1763"/>
+  <dimension ref="A1:E1764"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23707,8 +23707,19 @@
         <v>9490660</v>
       </c>
     </row>
+    <row r="1764" spans="1:3">
+      <c r="A1764" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1764">
+        <v>2962894</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1762">
+  <autoFilter ref="A1:E1763">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,50 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -263,10 +219,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -279,15 +236,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,22 +258,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,11 +287,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,67 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,13 +410,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +452,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,61 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,7 +575,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,8 +598,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,30 +645,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,167 +659,176 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1764"/>
+  <dimension ref="A1:E1765"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23718,8 +23718,19 @@
         <v>2962894</v>
       </c>
     </row>
+    <row r="1765" spans="1:3">
+      <c r="A1765" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1765">
+        <v>2386152</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1763">
+  <autoFilter ref="A1:E1764">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -205,31 +205,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -237,13 +220,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,7 +234,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,8 +255,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,6 +292,20 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -302,38 +324,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,6 +336,14 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +428,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,157 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,23 +604,37 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,37 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,152 +683,152 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1765"/>
+  <dimension ref="A1:E1766"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23729,8 +23729,19 @@
         <v>2386152</v>
       </c>
     </row>
+    <row r="1766" spans="1:3">
+      <c r="A1766" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1766">
+        <v>1215719</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1764">
+  <autoFilter ref="A1:E1765">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,18 +203,18 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -225,8 +225,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,14 +235,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,53 +251,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -341,9 +289,61 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +392,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +434,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,37 +470,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,7 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,19 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,69 +571,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -655,6 +596,36 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -668,167 +639,196 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1766"/>
+  <dimension ref="A1:E1767"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23740,8 +23740,19 @@
         <v>1215719</v>
       </c>
     </row>
+    <row r="1767" spans="1:3">
+      <c r="A1767" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1767">
+        <v>1345702</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1765">
+  <autoFilter ref="A1:E1766">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/楽天.xlsx
+++ b/dashboard/data/incoming/楽天.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1767</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,76 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,10 +226,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -309,15 +249,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -331,19 +294,56 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,25 +434,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,97 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,19 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,7 +575,70 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,51 +658,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -650,172 +668,154 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1767"/>
+  <dimension ref="A1:E1768"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23751,8 +23751,19 @@
         <v>1345702</v>
       </c>
     </row>
+    <row r="1768" spans="1:3">
+      <c r="A1768" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1768">
+        <v>2980687</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1766">
+  <autoFilter ref="A1:E1767">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
